--- a/stories/arbres/TREE-AUT-026.xlsx
+++ b/stories/arbres/TREE-AUT-026.xlsx
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -831,6 +831,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -845,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV87"/>
+  <dimension ref="A1:AW87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1139,6 +1151,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1301,6 +1318,11 @@
         <v>12</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Aujourd'hui, Lila est avec maman, à l'école. Lila a envie de jouer. maman est là, tout près. On va apprendre : Préparer son sac. Voici le geste : mettre dans le sac. Lila écoute maman. Lila entend les mots : sac, ce que l'adulte a dit.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1487,6 +1509,11 @@
         <v>12</v>
       </c>
       <c r="AV3" s="2" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le bac à sable, le toboggan, ou les balançoires.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1511,7 +1538,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Lila va vers le bac à sable. Un chat miaule une fois. maman sourit. Ici, c'est le bac à sable. Ce n'est pas comme les autres endroits. Lila se souvient : sac, ce que l'adulte a dit. Voici le geste : mettre dans le sac. On range un objet. maman dit : je suis là. On reste ensemble.</t>
+          <t>Lila va vers le bac à sable. Un chat miaule une fois. maman sourit. Ici, c'est le bac à sable. Ce n'est pas comme les autres endroits. Lila se souvient : sac, ce que l'adulte a dit. Voici le geste : mettre dans le sac. On range un objet. Je suis là. On reste ensemble.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1649,6 +1676,12 @@
         <v>12</v>
       </c>
       <c r="AV4" s="2" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Lila va vers le bac à sable. Un chat miaule une fois. maman sourit. Ici, c'est le bac à sable. Ce n'est pas comme les autres endroits. Lila se souvient : sac, ce que l'adulte a dit. Voici le geste : mettre dans le sac. On range un objet.
+maman|Je suis là. On reste ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1829,6 +1862,11 @@
       <c r="AV5" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Que fait-on ? Préparer son sac.</t>
         </is>
       </c>
     </row>
@@ -1997,6 +2035,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. Voici le geste : mettre dans le sac. Lila respire. Lila retient : sac, ce que l'adulte a dit. On continue, avec maman.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2183,6 +2226,11 @@
         <v>12</v>
       </c>
       <c r="AV7" s="2" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le ballon, le seau, ou le doudou.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2345,6 +2393,11 @@
         <v>12</v>
       </c>
       <c r="AV8" s="2" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>narrateur|Lila a choisi le ballon. La couverture est douce. Le ballon reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : mettre dans le sac. Lila répète tout bas : sac, ce que l'adulte a dit. On écoute jusqu'au bout. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2533,6 +2586,11 @@
       <c r="AV9" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -2697,6 +2755,11 @@
         <v>12</v>
       </c>
       <c r="AV10" s="2" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>narrateur|Lila rejoint Tom. Le vent est doux. On range un objet. Cette fin-là est celle de le bac à sable, le ballon et Tom. Lila a appris : Préparer son sac. Voici le geste : mettre dans le sac. Lila a entendu : sac, ce que l'adulte a dit. Lila dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2859,6 +2922,11 @@
         <v>12</v>
       </c>
       <c r="AV11" s="2" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3021,6 +3089,11 @@
         <v>12</v>
       </c>
       <c r="AV12" s="2" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>narrateur|Lila rejoint Léa. Le sol est un peu froid. On dit merci. Cette fin-là est celle de le bac à sable, le ballon et Léa. Lila a appris : Préparer son sac. Voici le geste : mettre dans le sac. Lila a entendu : sac, ce que l'adulte a dit. Lila dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3183,6 +3256,11 @@
         <v>12</v>
       </c>
       <c r="AV13" s="2" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3345,6 +3423,11 @@
         <v>12</v>
       </c>
       <c r="AV14" s="2" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>narrateur|Lila rejoint Sami. Une feuille tombe. On souffle doucement. Cette fin-là est celle de le bac à sable, le ballon et Sami. Lila a appris : Préparer son sac. Voici le geste : mettre dans le sac. Lila a entendu : sac, ce que l'adulte a dit. Lila dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3507,6 +3590,11 @@
         <v>12</v>
       </c>
       <c r="AV15" s="2" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3669,6 +3757,11 @@
         <v>12</v>
       </c>
       <c r="AV16" s="2" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>narrateur|Lila a choisi le seau. On entend un oiseau. Le seau reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : mettre dans le sac. Lila répète tout bas : sac, ce que l'adulte a dit. On attend son tour. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3857,6 +3950,11 @@
       <c r="AV17" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -4021,6 +4119,11 @@
         <v>12</v>
       </c>
       <c r="AV18" s="2" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>narrateur|Lila rejoint Tom. Le sol est un peu froid. On range un objet. Cette fin-là est celle de le bac à sable, le seau et Tom. Lila a appris : Préparer son sac. Voici le geste : mettre dans le sac. Lila a entendu : sac, ce que l'adulte a dit. Lila dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4183,6 +4286,11 @@
         <v>12</v>
       </c>
       <c r="AV19" s="2" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4345,6 +4453,11 @@
         <v>12</v>
       </c>
       <c r="AV20" s="2" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>narrateur|Lila rejoint Léa. Une feuille tombe. On dit merci. Cette fin-là est celle de le bac à sable, le seau et Léa. Lila a appris : Préparer son sac. Voici le geste : mettre dans le sac. Lila a entendu : sac, ce que l'adulte a dit. Lila dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4507,6 +4620,11 @@
         <v>12</v>
       </c>
       <c r="AV21" s="2" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4669,6 +4787,11 @@
         <v>12</v>
       </c>
       <c r="AV22" s="2" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>narrateur|Lila rejoint Sami. L'eau coule, tout petit bruit. On souffle doucement. Cette fin-là est celle de le bac à sable, le seau et Sami. Lila a appris : Préparer son sac. Voici le geste : mettre dans le sac. Lila a entendu : sac, ce que l'adulte a dit. Lila dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4831,6 +4954,11 @@
         <v>12</v>
       </c>
       <c r="AV23" s="2" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -4993,6 +5121,11 @@
         <v>12</v>
       </c>
       <c r="AV24" s="2" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>narrateur|Lila a choisi le doudou. Ça sent le pain chaud. Le doudou reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : mettre dans le sac. Lila répète tout bas : sac, ce que l'adulte a dit. On montre du doigt, sans courir. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5181,6 +5314,11 @@
       <c r="AV25" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -5345,6 +5483,11 @@
         <v>12</v>
       </c>
       <c r="AV26" s="2" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>narrateur|Lila rejoint Tom. Une feuille tombe. On range un objet. Cette fin-là est celle de le bac à sable, le doudou et Tom. Lila a appris : Préparer son sac. Voici le geste : mettre dans le sac. Lila a entendu : sac, ce que l'adulte a dit. Lila dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5507,6 +5650,11 @@
         <v>12</v>
       </c>
       <c r="AV27" s="2" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5669,6 +5817,11 @@
         <v>12</v>
       </c>
       <c r="AV28" s="2" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>narrateur|Lila rejoint Léa. L'eau coule, tout petit bruit. On dit merci. Cette fin-là est celle de le bac à sable, le doudou et Léa. Lila a appris : Préparer son sac. Voici le geste : mettre dans le sac. Lila a entendu : sac, ce que l'adulte a dit. Lila dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5831,6 +5984,11 @@
         <v>12</v>
       </c>
       <c r="AV29" s="2" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -5993,6 +6151,11 @@
         <v>12</v>
       </c>
       <c r="AV30" s="2" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>narrateur|Lila rejoint Sami. Un vélo passe au loin. On souffle doucement. Cette fin-là est celle de le bac à sable, le doudou et Sami. Lila a appris : Préparer son sac. Voici le geste : mettre dans le sac. Lila a entendu : sac, ce que l'adulte a dit. Lila dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6155,6 +6318,11 @@
         <v>12</v>
       </c>
       <c r="AV31" s="2" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6179,7 +6347,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Lila va vers le toboggan. Les chaussures font toc toc. maman sourit. Ici, c'est le toboggan. Ce n'est pas comme les autres endroits. Lila se souvient : sac, ce que l'adulte a dit. Voici le geste : mettre dans le sac. On dit merci. maman dit : je suis là. On reste ensemble.</t>
+          <t>Lila va vers le toboggan. Les chaussures font toc toc. maman sourit. Ici, c'est le toboggan. Ce n'est pas comme les autres endroits. Lila se souvient : sac, ce que l'adulte a dit. Voici le geste : mettre dans le sac. On dit merci. Je suis là. On reste ensemble.</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -6317,6 +6485,12 @@
         <v>12</v>
       </c>
       <c r="AV32" s="2" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>narrateur|Lila va vers le toboggan. Les chaussures font toc toc. maman sourit. Ici, c'est le toboggan. Ce n'est pas comme les autres endroits. Lila se souvient : sac, ce que l'adulte a dit. Voici le geste : mettre dans le sac. On dit merci.
+maman|Je suis là. On reste ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6497,6 +6671,11 @@
       <c r="AV33" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>narrateur|Que fait-on ? Préparer son sac.</t>
         </is>
       </c>
     </row>
@@ -6665,6 +6844,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. Voici le geste : mettre dans le sac. Lila respire. Lila retient : sac, ce que l'adulte a dit. On continue, avec maman.</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -6851,6 +7035,11 @@
         <v>12</v>
       </c>
       <c r="AV35" s="2" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le ballon, le seau, ou le doudou.</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -7013,6 +7202,11 @@
         <v>12</v>
       </c>
       <c r="AV36" s="2" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>narrateur|Lila a choisi le ballon. Le vent est doux. Le ballon reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : mettre dans le sac. Lila répète tout bas : sac, ce que l'adulte a dit. On écoute jusqu'au bout. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7201,6 +7395,11 @@
       <c r="AV37" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -7365,6 +7564,11 @@
         <v>12</v>
       </c>
       <c r="AV38" s="2" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>narrateur|Lila rejoint Tom. Le sol est un peu froid. On dit merci. Cette fin-là est celle de le toboggan, le ballon et Tom. Lila a appris : Préparer son sac. Voici le geste : mettre dans le sac. Lila a entendu : sac, ce que l'adulte a dit. Lila dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7527,6 +7731,11 @@
         <v>12</v>
       </c>
       <c r="AV39" s="2" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7689,6 +7898,11 @@
         <v>12</v>
       </c>
       <c r="AV40" s="2" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>narrateur|Lila rejoint Léa. Une feuille tombe. On souffle doucement. Cette fin-là est celle de le toboggan, le ballon et Léa. Lila a appris : Préparer son sac. Voici le geste : mettre dans le sac. Lila a entendu : sac, ce que l'adulte a dit. Lila dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -7851,6 +8065,11 @@
         <v>12</v>
       </c>
       <c r="AV41" s="2" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -8013,6 +8232,11 @@
         <v>12</v>
       </c>
       <c r="AV42" s="2" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>narrateur|Lila rejoint Sami. L'eau coule, tout petit bruit. On écoute jusqu'au bout. Cette fin-là est celle de le toboggan, le ballon et Sami. Lila a appris : Préparer son sac. Voici le geste : mettre dans le sac. Lila a entendu : sac, ce que l'adulte a dit. Lila dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8175,6 +8399,11 @@
         <v>12</v>
       </c>
       <c r="AV43" s="2" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8337,6 +8566,11 @@
         <v>12</v>
       </c>
       <c r="AV44" s="2" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>narrateur|Lila a choisi le seau. Le sol est un peu froid. Le seau reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : mettre dans le sac. Lila répète tout bas : sac, ce que l'adulte a dit. On attend son tour. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8525,6 +8759,11 @@
       <c r="AV45" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -8689,6 +8928,11 @@
         <v>12</v>
       </c>
       <c r="AV46" s="2" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>narrateur|Lila rejoint Tom. Une feuille tombe. On dit merci. Cette fin-là est celle de le toboggan, le seau et Tom. Lila a appris : Préparer son sac. Voici le geste : mettre dans le sac. Lila a entendu : sac, ce que l'adulte a dit. Lila dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -8851,6 +9095,11 @@
         <v>12</v>
       </c>
       <c r="AV47" s="2" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -9013,6 +9262,11 @@
         <v>12</v>
       </c>
       <c r="AV48" s="2" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>narrateur|Lila rejoint Léa. L'eau coule, tout petit bruit. On souffle doucement. Cette fin-là est celle de le toboggan, le seau et Léa. Lila a appris : Préparer son sac. Voici le geste : mettre dans le sac. Lila a entendu : sac, ce que l'adulte a dit. Lila dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9175,6 +9429,11 @@
         <v>12</v>
       </c>
       <c r="AV49" s="2" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9337,6 +9596,11 @@
         <v>12</v>
       </c>
       <c r="AV50" s="2" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>narrateur|Lila rejoint Sami. Un vélo passe au loin. On écoute jusqu'au bout. Cette fin-là est celle de le toboggan, le seau et Sami. Lila a appris : Préparer son sac. Voici le geste : mettre dans le sac. Lila a entendu : sac, ce que l'adulte a dit. Lila dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9499,6 +9763,11 @@
         <v>12</v>
       </c>
       <c r="AV51" s="2" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9661,6 +9930,11 @@
         <v>12</v>
       </c>
       <c r="AV52" s="2" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>narrateur|Lila a choisi le doudou. Une feuille tombe. Le doudou reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : mettre dans le sac. Lila répète tout bas : sac, ce que l'adulte a dit. On montre du doigt, sans courir. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -9849,6 +10123,11 @@
       <c r="AV53" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -10013,6 +10292,11 @@
         <v>12</v>
       </c>
       <c r="AV54" s="2" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>narrateur|Lila rejoint Tom. L'eau coule, tout petit bruit. On dit merci. Cette fin-là est celle de le toboggan, le doudou et Tom. Lila a appris : Préparer son sac. Voici le geste : mettre dans le sac. Lila a entendu : sac, ce que l'adulte a dit. Lila dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10175,6 +10459,11 @@
         <v>12</v>
       </c>
       <c r="AV55" s="2" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10337,6 +10626,11 @@
         <v>12</v>
       </c>
       <c r="AV56" s="2" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>narrateur|Lila rejoint Léa. Un vélo passe au loin. On souffle doucement. Cette fin-là est celle de le toboggan, le doudou et Léa. Lila a appris : Préparer son sac. Voici le geste : mettre dans le sac. Lila a entendu : sac, ce que l'adulte a dit. Lila dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10499,6 +10793,11 @@
         <v>12</v>
       </c>
       <c r="AV57" s="2" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10661,6 +10960,11 @@
         <v>12</v>
       </c>
       <c r="AV58" s="2" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>narrateur|Lila rejoint Sami. La lumière est claire. On écoute jusqu'au bout. Cette fin-là est celle de le toboggan, le doudou et Sami. Lila a appris : Préparer son sac. Voici le geste : mettre dans le sac. Lila a entendu : sac, ce que l'adulte a dit. Lila dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -10823,6 +11127,11 @@
         <v>12</v>
       </c>
       <c r="AV59" s="2" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -10847,7 +11156,7 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>Lila va vers les balançoires. La couverture est douce. maman sourit. Ici, c'est les balançoires. Ce n'est pas comme les autres endroits. Lila se souvient : sac, ce que l'adulte a dit. Voici le geste : mettre dans le sac. On souffle doucement. maman dit : je suis là. On reste ensemble.</t>
+          <t>Lila va vers les balançoires. La couverture est douce. maman sourit. Ici, c'est les balançoires. Ce n'est pas comme les autres endroits. Lila se souvient : sac, ce que l'adulte a dit. Voici le geste : mettre dans le sac. On souffle doucement. Je suis là. On reste ensemble.</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
@@ -10985,6 +11294,12 @@
         <v>12</v>
       </c>
       <c r="AV60" s="2" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>narrateur|Lila va vers les balançoires. La couverture est douce. maman sourit. Ici, c'est les balançoires. Ce n'est pas comme les autres endroits. Lila se souvient : sac, ce que l'adulte a dit. Voici le geste : mettre dans le sac. On souffle doucement.
+maman|Je suis là. On reste ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11165,6 +11480,11 @@
       <c r="AV61" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>narrateur|Que fait-on ? Préparer son sac.</t>
         </is>
       </c>
     </row>
@@ -11333,6 +11653,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. Voici le geste : mettre dans le sac. Lila respire. Lila retient : sac, ce que l'adulte a dit. On continue, avec maman.</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11519,6 +11844,11 @@
         <v>12</v>
       </c>
       <c r="AV63" s="2" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le ballon, le seau, ou le doudou.</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -11681,6 +12011,11 @@
         <v>12</v>
       </c>
       <c r="AV64" s="2" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>narrateur|Lila a choisi le ballon. L'eau coule, tout petit bruit. Le ballon reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : mettre dans le sac. Lila répète tout bas : sac, ce que l'adulte a dit. On écoute jusqu'au bout. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -11869,6 +12204,11 @@
       <c r="AV65" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -12033,6 +12373,11 @@
         <v>12</v>
       </c>
       <c r="AV66" s="2" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>narrateur|Lila rejoint Tom. Une feuille tombe. On souffle doucement. Cette fin-là est celle de les balançoires, le ballon et Tom. Lila a appris : Préparer son sac. Voici le geste : mettre dans le sac. Lila a entendu : sac, ce que l'adulte a dit. Lila dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12195,6 +12540,11 @@
         <v>12</v>
       </c>
       <c r="AV67" s="2" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12357,6 +12707,11 @@
         <v>12</v>
       </c>
       <c r="AV68" s="2" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>narrateur|Lila rejoint Léa. L'eau coule, tout petit bruit. On écoute jusqu'au bout. Cette fin-là est celle de les balançoires, le ballon et Léa. Lila a appris : Préparer son sac. Voici le geste : mettre dans le sac. Lila a entendu : sac, ce que l'adulte a dit. Lila dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12519,6 +12874,11 @@
         <v>12</v>
       </c>
       <c r="AV69" s="2" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -12681,6 +13041,11 @@
         <v>12</v>
       </c>
       <c r="AV70" s="2" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>narrateur|Lila rejoint Sami. Un vélo passe au loin. On attend son tour. Cette fin-là est celle de les balançoires, le ballon et Sami. Lila a appris : Préparer son sac. Voici le geste : mettre dans le sac. Lila a entendu : sac, ce que l'adulte a dit. Lila dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -12843,6 +13208,11 @@
         <v>12</v>
       </c>
       <c r="AV71" s="2" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -13005,6 +13375,11 @@
         <v>12</v>
       </c>
       <c r="AV72" s="2" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>narrateur|Lila a choisi le seau. Un vélo passe au loin. Le seau reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : mettre dans le sac. Lila répète tout bas : sac, ce que l'adulte a dit. On attend son tour. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13193,6 +13568,11 @@
       <c r="AV73" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -13357,6 +13737,11 @@
         <v>12</v>
       </c>
       <c r="AV74" s="2" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>narrateur|Lila rejoint Tom. L'eau coule, tout petit bruit. On souffle doucement. Cette fin-là est celle de les balançoires, le seau et Tom. Lila a appris : Préparer son sac. Voici le geste : mettre dans le sac. Lila a entendu : sac, ce que l'adulte a dit. Lila dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13519,6 +13904,11 @@
         <v>12</v>
       </c>
       <c r="AV75" s="2" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -13681,6 +14071,11 @@
         <v>12</v>
       </c>
       <c r="AV76" s="2" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>narrateur|Lila rejoint Léa. Un vélo passe au loin. On écoute jusqu'au bout. Cette fin-là est celle de les balançoires, le seau et Léa. Lila a appris : Préparer son sac. Voici le geste : mettre dans le sac. Lila a entendu : sac, ce que l'adulte a dit. Lila dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -13843,6 +14238,11 @@
         <v>12</v>
       </c>
       <c r="AV77" s="2" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -14005,6 +14405,11 @@
         <v>12</v>
       </c>
       <c r="AV78" s="2" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>narrateur|Lila rejoint Sami. La lumière est claire. On attend son tour. Cette fin-là est celle de les balançoires, le seau et Sami. Lila a appris : Préparer son sac. Voici le geste : mettre dans le sac. Lila a entendu : sac, ce que l'adulte a dit. Lila dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14167,6 +14572,11 @@
         <v>12</v>
       </c>
       <c r="AV79" s="2" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14329,6 +14739,11 @@
         <v>12</v>
       </c>
       <c r="AV80" s="2" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>narrateur|Lila a choisi le doudou. La lumière est claire. Le doudou reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : mettre dans le sac. Lila répète tout bas : sac, ce que l'adulte a dit. On montre du doigt, sans courir. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14517,6 +14932,11 @@
       <c r="AV81" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -14681,6 +15101,11 @@
         <v>12</v>
       </c>
       <c r="AV82" s="2" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>narrateur|Lila rejoint Tom. Un vélo passe au loin. On souffle doucement. Cette fin-là est celle de les balançoires, le doudou et Tom. Lila a appris : Préparer son sac. Voici le geste : mettre dans le sac. Lila a entendu : sac, ce que l'adulte a dit. Lila dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -14843,6 +15268,11 @@
         <v>12</v>
       </c>
       <c r="AV83" s="2" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -15005,6 +15435,11 @@
         <v>12</v>
       </c>
       <c r="AV84" s="2" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>narrateur|Lila rejoint Léa. La lumière est claire. On écoute jusqu'au bout. Cette fin-là est celle de les balançoires, le doudou et Léa. Lila a appris : Préparer son sac. Voici le geste : mettre dans le sac. Lila a entendu : sac, ce que l'adulte a dit. Lila dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15167,6 +15602,11 @@
         <v>12</v>
       </c>
       <c r="AV85" s="2" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15329,6 +15769,11 @@
         <v>12</v>
       </c>
       <c r="AV86" s="2" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>narrateur|Lila rejoint Sami. Il y a des miettes sur la table. On attend son tour. Cette fin-là est celle de les balançoires, le doudou et Sami. Lila a appris : Préparer son sac. Voici le geste : mettre dans le sac. Lila a entendu : sac, ce que l'adulte a dit. Lila dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15491,6 +15936,11 @@
         <v>12</v>
       </c>
       <c r="AV87" s="2" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15509,7 +15959,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A10"/>
+  <dimension ref="A1:A11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -15582,6 +16032,13 @@
       <c r="A10" t="inlineStr">
         <is>
           <t>ch3C3: prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/TREE-AUT-026.xlsx
+++ b/stories/arbres/TREE-AUT-026.xlsx
@@ -857,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW87"/>
+  <dimension ref="A1:AX87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1156,6 +1156,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1323,6 +1328,7 @@
           <t>narrateur|Aujourd'hui, Lila est avec maman, à l'école. Lila a envie de jouer. maman est là, tout près. On va apprendre : Préparer son sac. Voici le geste : mettre dans le sac. Lila écoute maman. Lila entend les mots : sac, ce que l'adulte a dit.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1514,6 +1520,7 @@
           <t>narrateur|On peut prendre le bac à sable, le toboggan, ou les balançoires.</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1682,6 +1689,7 @@
 maman|Je suis là. On reste ensemble.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1869,6 +1877,7 @@
           <t>narrateur|Que fait-on ? Préparer son sac.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2040,6 +2049,7 @@
           <t>narrateur|Oui. Voici le geste : mettre dans le sac. Lila respire. Lila retient : sac, ce que l'adulte a dit. On continue, avec maman.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2231,6 +2241,7 @@
           <t>narrateur|On peut prendre le ballon, le seau, ou le doudou.</t>
         </is>
       </c>
+      <c r="AX7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2398,6 +2409,7 @@
           <t>narrateur|Lila a choisi le ballon. La couverture est douce. Le ballon reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : mettre dans le sac. Lila répète tout bas : sac, ce que l'adulte a dit. On écoute jusqu'au bout. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2593,6 +2605,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2760,6 +2773,7 @@
           <t>narrateur|Lila rejoint Tom. Le vent est doux. On range un objet. Cette fin-là est celle de le bac à sable, le ballon et Tom. Lila a appris : Préparer son sac. Voici le geste : mettre dans le sac. Lila a entendu : sac, ce que l'adulte a dit. Lila dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2927,6 +2941,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3094,6 +3109,7 @@
           <t>narrateur|Lila rejoint Léa. Le sol est un peu froid. On dit merci. Cette fin-là est celle de le bac à sable, le ballon et Léa. Lila a appris : Préparer son sac. Voici le geste : mettre dans le sac. Lila a entendu : sac, ce que l'adulte a dit. Lila dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3261,6 +3277,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3428,6 +3445,7 @@
           <t>narrateur|Lila rejoint Sami. Une feuille tombe. On souffle doucement. Cette fin-là est celle de le bac à sable, le ballon et Sami. Lila a appris : Préparer son sac. Voici le geste : mettre dans le sac. Lila a entendu : sac, ce que l'adulte a dit. Lila dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3595,6 +3613,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3762,6 +3781,7 @@
           <t>narrateur|Lila a choisi le seau. On entend un oiseau. Le seau reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : mettre dans le sac. Lila répète tout bas : sac, ce que l'adulte a dit. On attend son tour. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3957,6 +3977,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -4124,6 +4145,7 @@
           <t>narrateur|Lila rejoint Tom. Le sol est un peu froid. On range un objet. Cette fin-là est celle de le bac à sable, le seau et Tom. Lila a appris : Préparer son sac. Voici le geste : mettre dans le sac. Lila a entendu : sac, ce que l'adulte a dit. Lila dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4291,6 +4313,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4458,6 +4481,7 @@
           <t>narrateur|Lila rejoint Léa. Une feuille tombe. On dit merci. Cette fin-là est celle de le bac à sable, le seau et Léa. Lila a appris : Préparer son sac. Voici le geste : mettre dans le sac. Lila a entendu : sac, ce que l'adulte a dit. Lila dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4625,6 +4649,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4792,6 +4817,7 @@
           <t>narrateur|Lila rejoint Sami. L'eau coule, tout petit bruit. On souffle doucement. Cette fin-là est celle de le bac à sable, le seau et Sami. Lila a appris : Préparer son sac. Voici le geste : mettre dans le sac. Lila a entendu : sac, ce que l'adulte a dit. Lila dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4959,6 +4985,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -5126,6 +5153,7 @@
           <t>narrateur|Lila a choisi le doudou. Ça sent le pain chaud. Le doudou reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : mettre dans le sac. Lila répète tout bas : sac, ce que l'adulte a dit. On montre du doigt, sans courir. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5321,6 +5349,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5488,6 +5517,7 @@
           <t>narrateur|Lila rejoint Tom. Une feuille tombe. On range un objet. Cette fin-là est celle de le bac à sable, le doudou et Tom. Lila a appris : Préparer son sac. Voici le geste : mettre dans le sac. Lila a entendu : sac, ce que l'adulte a dit. Lila dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5655,6 +5685,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5822,6 +5853,7 @@
           <t>narrateur|Lila rejoint Léa. L'eau coule, tout petit bruit. On dit merci. Cette fin-là est celle de le bac à sable, le doudou et Léa. Lila a appris : Préparer son sac. Voici le geste : mettre dans le sac. Lila a entendu : sac, ce que l'adulte a dit. Lila dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5989,6 +6021,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -6156,6 +6189,7 @@
           <t>narrateur|Lila rejoint Sami. Un vélo passe au loin. On souffle doucement. Cette fin-là est celle de le bac à sable, le doudou et Sami. Lila a appris : Préparer son sac. Voici le geste : mettre dans le sac. Lila a entendu : sac, ce que l'adulte a dit. Lila dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6323,6 +6357,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6491,6 +6526,7 @@
 maman|Je suis là. On reste ensemble.</t>
         </is>
       </c>
+      <c r="AX32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6678,6 +6714,7 @@
           <t>narrateur|Que fait-on ? Préparer son sac.</t>
         </is>
       </c>
+      <c r="AX33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -6849,6 +6886,7 @@
           <t>narrateur|Oui. Voici le geste : mettre dans le sac. Lila respire. Lila retient : sac, ce que l'adulte a dit. On continue, avec maman.</t>
         </is>
       </c>
+      <c r="AX34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -7040,6 +7078,7 @@
           <t>narrateur|On peut prendre le ballon, le seau, ou le doudou.</t>
         </is>
       </c>
+      <c r="AX35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -7207,6 +7246,7 @@
           <t>narrateur|Lila a choisi le ballon. Le vent est doux. Le ballon reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : mettre dans le sac. Lila répète tout bas : sac, ce que l'adulte a dit. On écoute jusqu'au bout. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7402,6 +7442,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7569,6 +7610,7 @@
           <t>narrateur|Lila rejoint Tom. Le sol est un peu froid. On dit merci. Cette fin-là est celle de le toboggan, le ballon et Tom. Lila a appris : Préparer son sac. Voici le geste : mettre dans le sac. Lila a entendu : sac, ce que l'adulte a dit. Lila dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7736,6 +7778,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7903,6 +7946,7 @@
           <t>narrateur|Lila rejoint Léa. Une feuille tombe. On souffle doucement. Cette fin-là est celle de le toboggan, le ballon et Léa. Lila a appris : Préparer son sac. Voici le geste : mettre dans le sac. Lila a entendu : sac, ce que l'adulte a dit. Lila dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -8070,6 +8114,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -8237,6 +8282,7 @@
           <t>narrateur|Lila rejoint Sami. L'eau coule, tout petit bruit. On écoute jusqu'au bout. Cette fin-là est celle de le toboggan, le ballon et Sami. Lila a appris : Préparer son sac. Voici le geste : mettre dans le sac. Lila a entendu : sac, ce que l'adulte a dit. Lila dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8404,6 +8450,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8571,6 +8618,7 @@
           <t>narrateur|Lila a choisi le seau. Le sol est un peu froid. Le seau reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : mettre dans le sac. Lila répète tout bas : sac, ce que l'adulte a dit. On attend son tour. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8766,6 +8814,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -8933,6 +8982,7 @@
           <t>narrateur|Lila rejoint Tom. Une feuille tombe. On dit merci. Cette fin-là est celle de le toboggan, le seau et Tom. Lila a appris : Préparer son sac. Voici le geste : mettre dans le sac. Lila a entendu : sac, ce que l'adulte a dit. Lila dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -9100,6 +9150,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -9267,6 +9318,7 @@
           <t>narrateur|Lila rejoint Léa. L'eau coule, tout petit bruit. On souffle doucement. Cette fin-là est celle de le toboggan, le seau et Léa. Lila a appris : Préparer son sac. Voici le geste : mettre dans le sac. Lila a entendu : sac, ce que l'adulte a dit. Lila dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9434,6 +9486,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9601,6 +9654,7 @@
           <t>narrateur|Lila rejoint Sami. Un vélo passe au loin. On écoute jusqu'au bout. Cette fin-là est celle de le toboggan, le seau et Sami. Lila a appris : Préparer son sac. Voici le geste : mettre dans le sac. Lila a entendu : sac, ce que l'adulte a dit. Lila dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9768,6 +9822,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9935,6 +9990,7 @@
           <t>narrateur|Lila a choisi le doudou. Une feuille tombe. Le doudou reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : mettre dans le sac. Lila répète tout bas : sac, ce que l'adulte a dit. On montre du doigt, sans courir. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -10130,6 +10186,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -10297,6 +10354,7 @@
           <t>narrateur|Lila rejoint Tom. L'eau coule, tout petit bruit. On dit merci. Cette fin-là est celle de le toboggan, le doudou et Tom. Lila a appris : Préparer son sac. Voici le geste : mettre dans le sac. Lila a entendu : sac, ce que l'adulte a dit. Lila dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10464,6 +10522,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10631,6 +10690,7 @@
           <t>narrateur|Lila rejoint Léa. Un vélo passe au loin. On souffle doucement. Cette fin-là est celle de le toboggan, le doudou et Léa. Lila a appris : Préparer son sac. Voici le geste : mettre dans le sac. Lila a entendu : sac, ce que l'adulte a dit. Lila dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10798,6 +10858,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10965,6 +11026,7 @@
           <t>narrateur|Lila rejoint Sami. La lumière est claire. On écoute jusqu'au bout. Cette fin-là est celle de le toboggan, le doudou et Sami. Lila a appris : Préparer son sac. Voici le geste : mettre dans le sac. Lila a entendu : sac, ce que l'adulte a dit. Lila dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -11132,6 +11194,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -11300,6 +11363,7 @@
 maman|Je suis là. On reste ensemble.</t>
         </is>
       </c>
+      <c r="AX60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11487,6 +11551,7 @@
           <t>narrateur|Que fait-on ? Préparer son sac.</t>
         </is>
       </c>
+      <c r="AX61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -11658,6 +11723,7 @@
           <t>narrateur|Oui. Voici le geste : mettre dans le sac. Lila respire. Lila retient : sac, ce que l'adulte a dit. On continue, avec maman.</t>
         </is>
       </c>
+      <c r="AX62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11849,6 +11915,7 @@
           <t>narrateur|On peut prendre le ballon, le seau, ou le doudou.</t>
         </is>
       </c>
+      <c r="AX63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -12016,6 +12083,7 @@
           <t>narrateur|Lila a choisi le ballon. L'eau coule, tout petit bruit. Le ballon reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : mettre dans le sac. Lila répète tout bas : sac, ce que l'adulte a dit. On écoute jusqu'au bout. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -12211,6 +12279,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -12378,6 +12447,7 @@
           <t>narrateur|Lila rejoint Tom. Une feuille tombe. On souffle doucement. Cette fin-là est celle de les balançoires, le ballon et Tom. Lila a appris : Préparer son sac. Voici le geste : mettre dans le sac. Lila a entendu : sac, ce que l'adulte a dit. Lila dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12545,6 +12615,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12712,6 +12783,7 @@
           <t>narrateur|Lila rejoint Léa. L'eau coule, tout petit bruit. On écoute jusqu'au bout. Cette fin-là est celle de les balançoires, le ballon et Léa. Lila a appris : Préparer son sac. Voici le geste : mettre dans le sac. Lila a entendu : sac, ce que l'adulte a dit. Lila dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12879,6 +12951,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -13046,6 +13119,7 @@
           <t>narrateur|Lila rejoint Sami. Un vélo passe au loin. On attend son tour. Cette fin-là est celle de les balançoires, le ballon et Sami. Lila a appris : Préparer son sac. Voici le geste : mettre dans le sac. Lila a entendu : sac, ce que l'adulte a dit. Lila dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -13213,6 +13287,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -13380,6 +13455,7 @@
           <t>narrateur|Lila a choisi le seau. Un vélo passe au loin. Le seau reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : mettre dans le sac. Lila répète tout bas : sac, ce que l'adulte a dit. On attend son tour. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13575,6 +13651,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -13742,6 +13819,7 @@
           <t>narrateur|Lila rejoint Tom. L'eau coule, tout petit bruit. On souffle doucement. Cette fin-là est celle de les balançoires, le seau et Tom. Lila a appris : Préparer son sac. Voici le geste : mettre dans le sac. Lila a entendu : sac, ce que l'adulte a dit. Lila dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13909,6 +13987,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -14076,6 +14155,7 @@
           <t>narrateur|Lila rejoint Léa. Un vélo passe au loin. On écoute jusqu'au bout. Cette fin-là est celle de les balançoires, le seau et Léa. Lila a appris : Préparer son sac. Voici le geste : mettre dans le sac. Lila a entendu : sac, ce que l'adulte a dit. Lila dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -14243,6 +14323,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -14410,6 +14491,7 @@
           <t>narrateur|Lila rejoint Sami. La lumière est claire. On attend son tour. Cette fin-là est celle de les balançoires, le seau et Sami. Lila a appris : Préparer son sac. Voici le geste : mettre dans le sac. Lila a entendu : sac, ce que l'adulte a dit. Lila dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14577,6 +14659,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14744,6 +14827,7 @@
           <t>narrateur|Lila a choisi le doudou. La lumière est claire. Le doudou reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : mettre dans le sac. Lila répète tout bas : sac, ce que l'adulte a dit. On montre du doigt, sans courir. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14939,6 +15023,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -15106,6 +15191,7 @@
           <t>narrateur|Lila rejoint Tom. Un vélo passe au loin. On souffle doucement. Cette fin-là est celle de les balançoires, le doudou et Tom. Lila a appris : Préparer son sac. Voici le geste : mettre dans le sac. Lila a entendu : sac, ce que l'adulte a dit. Lila dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -15273,6 +15359,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -15440,6 +15527,7 @@
           <t>narrateur|Lila rejoint Léa. La lumière est claire. On écoute jusqu'au bout. Cette fin-là est celle de les balançoires, le doudou et Léa. Lila a appris : Préparer son sac. Voici le geste : mettre dans le sac. Lila a entendu : sac, ce que l'adulte a dit. Lila dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15607,6 +15695,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15774,6 +15863,7 @@
           <t>narrateur|Lila rejoint Sami. Il y a des miettes sur la table. On attend son tour. Cette fin-là est celle de les balançoires, le doudou et Sami. Lila a appris : Préparer son sac. Voici le geste : mettre dans le sac. Lila a entendu : sac, ce que l'adulte a dit. Lila dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15941,6 +16031,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX87" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15959,7 +16050,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A11"/>
+  <dimension ref="A1:A13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -16039,6 +16130,20 @@
       <c r="A11" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -16053,7 +16158,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -16240,6 +16345,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/TREE-AUT-026.xlsx
+++ b/stories/arbres/TREE-AUT-026.xlsx
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -552,7 +552,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Préparer son sac — à l'école</t>
+          <t>Le cartable jaune de Sarah</t>
         </is>
       </c>
     </row>
@@ -843,6 +843,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Sarah prépare son cartable jaune. Papa et maman disent ce qu'elle met. Goûter, cahier ou gourde, puis palier, portemanteau ou banc, puis crayon, mouchoir ou livre.</t>
         </is>
       </c>
     </row>
@@ -1185,7 +1197,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Aujourd'hui, Lila est avec maman, à l'école. Lila a envie de jouer. maman est là, tout près. On va apprendre : Préparer son sac. Voici le geste : mettre dans le sac. Lila écoute maman. Lila entend les mots : sac, ce que l'adulte a dit.</t>
+          <t>La dernière marche de l'escalier craque. Un cartable jaune est posé dessus. La boucle du cartable brille. Une peau d'orange sent fort. Elle est dans la cuisine. Loin, la cloche de l'école fait ding. Les crochets du portemanteau sont vides. Ils attendent les manteaux. Une craie blanche a glissé. Elle est sous le banc de l'entrée. Le soleil fait un rectangle. Le rectangle est sur le carrelage. Le cartable est là, Sarah. On met dans le sac ce que maman a dit. Ou ce que papa a dit. Sarah pose la main sur le cartable. Le tissu est un peu rêche. En ce moment, le sac est encore vide. Je veux l'école ! D'accord. On prépare le sac d'abord. On met ce que l'adulte a dit. Sarah ouvre un peu la boucle. Ça fait tchac. Tu as entendu la cloche ? Oui, maman. Bravo. On commence.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1325,10 +1337,41 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Aujourd'hui, Lila est avec maman, à l'école. Lila a envie de jouer. maman est là, tout près. On va apprendre : Préparer son sac. Voici le geste : mettre dans le sac. Lila écoute maman. Lila entend les mots : sac, ce que l'adulte a dit.</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr"/>
+          <t>narrateur|La dernière marche de l'escalier craque.
+narrateur|Un cartable jaune est posé dessus.
+narrateur|La boucle du cartable brille.
+narrateur|Une peau d'orange sent fort.
+narrateur|Elle est dans la cuisine.
+narrateur|Loin, la cloche de l'école fait ding.
+narrateur|Les crochets du portemanteau sont vides.
+narrateur|Ils attendent les manteaux.
+narrateur|Une craie blanche a glissé.
+narrateur|Elle est sous le banc de l'entrée.
+narrateur|Le soleil fait un rectangle.
+narrateur|Le rectangle est sur le carrelage.
+maman|Le cartable est là, Sarah.
+papa|On met dans le sac ce que maman a dit.
+papa|Ou ce que papa a dit.
+narrateur|Sarah pose la main sur le cartable.
+narrateur|Le tissu est un peu rêche.
+narrateur|En ce moment, le sac est encore vide.
+enfant-f|Je veux l'école !
+maman|D'accord.
+maman|On prépare le sac d'abord.
+papa|On met ce que l'adulte a dit.
+narrateur|Sarah ouvre un peu la boucle.
+narrateur|Ça fait tchac.
+maman|Tu as entendu la cloche ?
+enfant-f|Oui, maman.
+papa|Bravo.
+papa|On commence.</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>escalier,sac,cloche</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1353,7 +1396,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le bac à sable, le toboggan, ou les balançoires.</t>
+          <t>On peut mettre le goûter, le cahier, ou la gourde.</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1517,7 +1560,7 @@
       <c r="AV3" s="2" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le bac à sable, le toboggan, ou les balançoires.</t>
+          <t>narrateur|On peut mettre le goûter, le cahier, ou la gourde.</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr"/>
@@ -1545,7 +1588,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Lila va vers le bac à sable. Un chat miaule une fois. maman sourit. Ici, c'est le bac à sable. Ce n'est pas comme les autres endroits. Lila se souvient : sac, ce que l'adulte a dit. Voici le geste : mettre dans le sac. On range un objet. Je suis là. On reste ensemble.</t>
+          <t>Le goûter est dans un papier. Le papier craque un peu. Ça sent l'orange et le biscuit. Le goûter dans le sac, Sarah. Le goûter. Sarah le prend à deux mains. Elle le glisse dans le sac. Le fond du sac fait un bruit doux. Bravo. Tu as mis ce que maman a dit. Tu as fini de mettre le goûter ? Oui. Le papier reste un peu froissé. Le sac a ce que l'adulte a dit.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1685,11 +1728,27 @@
       <c r="AV4" s="2" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Lila va vers le bac à sable. Un chat miaule une fois. maman sourit. Ici, c'est le bac à sable. Ce n'est pas comme les autres endroits. Lila se souvient : sac, ce que l'adulte a dit. Voici le geste : mettre dans le sac. On range un objet.
-maman|Je suis là. On reste ensemble.</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr"/>
+          <t>narrateur|Le goûter est dans un papier.
+narrateur|Le papier craque un peu.
+narrateur|Ça sent l'orange et le biscuit.
+maman|Le goûter dans le sac, Sarah.
+enfant-f|Le goûter.
+narrateur|Sarah le prend à deux mains.
+narrateur|Elle le glisse dans le sac.
+narrateur|Le fond du sac fait un bruit doux.
+papa|Bravo.
+papa|Tu as mis ce que maman a dit.
+maman|Tu as fini de mettre le goûter ?
+enfant-f|Oui.
+narrateur|Le papier reste un peu froissé.
+papa|Le sac a ce que l'adulte a dit.</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>papier</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1714,7 +1773,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Que fait-on ? Préparer son sac.</t>
+          <t>On met quoi dans le sac ?</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1874,7 +1933,7 @@
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Que fait-on ? Préparer son sac.</t>
+          <t>narrateur|On met quoi dans le sac ?</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr"/>
@@ -1902,7 +1961,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Oui. Voici le geste : mettre dans le sac. Lila respire. Lila retient : sac, ce que l'adulte a dit. On continue, avec maman.</t>
+          <t>Oui. On met dans le sac ce que maman a dit. Ou ce que papa a dit. Bravo, Sarah. Tu as écouté. C'est du bon travail. Le sac a ce que l'adulte a dit. Le goûter est dedans. On continue ensemble ? Oui.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2046,7 +2105,16 @@
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|Oui. Voici le geste : mettre dans le sac. Lila respire. Lila retient : sac, ce que l'adulte a dit. On continue, avec maman.</t>
+          <t>narrateur|Oui.
+narrateur|On met dans le sac ce que maman a dit.
+narrateur|Ou ce que papa a dit.
+maman|Bravo, Sarah.
+maman|Tu as écouté.
+papa|C'est du bon travail.
+papa|Le sac a ce que l'adulte a dit.
+enfant-f|Le goûter est dedans.
+maman|On continue ensemble ?
+enfant-f|Oui.</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr"/>
@@ -2074,7 +2142,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le ballon, le seau, ou le doudou.</t>
+          <t>On peut aller au palier, au portemanteau, ou au banc.</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -2238,7 +2306,7 @@
       <c r="AV7" s="2" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le ballon, le seau, ou le doudou.</t>
+          <t>narrateur|On peut aller au palier, au portemanteau, ou au banc.</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr"/>
@@ -2266,7 +2334,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Lila a choisi le ballon. La couverture est douce. Le ballon reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : mettre dans le sac. Lila répète tout bas : sac, ce que l'adulte a dit. On écoute jusqu'au bout. papa n'est pas loin.</t>
+          <t>Sarah monte le sac au palier. La marche craque encore. Le bois est un peu froid. Le palier, Sarah. On pose le sac un moment. Sarah pose le cartable jaune. Le goûter est déjà dedans. Bravo. Tu as mis ce que maman a dit. Le sac reste près de toi ? Oui. La cloche de l'école est plus loin.</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -2406,10 +2474,25 @@
       <c r="AV8" s="2" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>narrateur|Lila a choisi le ballon. La couverture est douce. Le ballon reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : mettre dans le sac. Lila répète tout bas : sac, ce que l'adulte a dit. On écoute jusqu'au bout. papa n'est pas loin.</t>
-        </is>
-      </c>
-      <c r="AX8" t="inlineStr"/>
+          <t>narrateur|Sarah monte le sac au palier.
+narrateur|La marche craque encore.
+narrateur|Le bois est un peu froid.
+maman|Le palier, Sarah.
+maman|On pose le sac un moment.
+narrateur|Sarah pose le cartable jaune.
+narrateur|Le goûter est déjà dedans.
+papa|Bravo.
+papa|Tu as mis ce que maman a dit.
+maman|Le sac reste près de toi ?
+enfant-f|Oui.
+narrateur|La cloche de l'école est plus loin.</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>escalier</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2434,7 +2517,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre Tom, Léa, ou Sami.</t>
+          <t>On peut prendre le crayon, le mouchoir, ou le livre.</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -2602,7 +2685,7 @@
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
+          <t>narrateur|On peut prendre le crayon, le mouchoir, ou le livre.</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr"/>
@@ -2630,7 +2713,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Lila rejoint Tom. Le vent est doux. On range un objet. Cette fin-là est celle de le bac à sable, le ballon et Tom. Lila a appris : Préparer son sac. Voici le geste : mettre dans le sac. Lila a entendu : sac, ce que l'adulte a dit. Lila dit merci à maman. On rentre.</t>
+          <t>Au palier, un crayon jaune attend. Il sent le bois. La mine est bien taillée. Le crayon dans le sac, Sarah. Le crayon. Sarah le glisse près du bord. Bravo. Tu as mis ce que maman a dit. Le goûter est déjà dedans. Le sac a ce que l'adulte a dit. Tu as fini le crayon ? Oui, papa. La marche craque un tout petit peu.</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -2770,10 +2853,26 @@
       <c r="AV10" s="2" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>narrateur|Lila rejoint Tom. Le vent est doux. On range un objet. Cette fin-là est celle de le bac à sable, le ballon et Tom. Lila a appris : Préparer son sac. Voici le geste : mettre dans le sac. Lila a entendu : sac, ce que l'adulte a dit. Lila dit merci à maman. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX10" t="inlineStr"/>
+          <t>narrateur|Au palier, un crayon jaune attend.
+narrateur|Il sent le bois.
+narrateur|La mine est bien taillée.
+maman|Le crayon dans le sac, Sarah.
+enfant-f|Le crayon.
+narrateur|Sarah le glisse près du bord.
+papa|Bravo.
+papa|Tu as mis ce que maman a dit.
+narrateur|Le goûter est déjà dedans.
+maman|Le sac a ce que l'adulte a dit.
+papa|Tu as fini le crayon ?
+enfant-f|Oui, papa.
+narrateur|La marche craque un tout petit peu.</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>crayon</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2798,7 +2897,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Sarah ferme le sac. Ça fait zzz. Le sac est prêt. Bravo, Sarah. Tu as fait du bon travail. Tu as mis le goûter. Et le crayon. C'est ce que l'adulte a dit. Merci. Ils restent un moment près de le palier. La marche de l'escalier ne craque plus. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -2938,7 +3037,18 @@
       <c r="AV11" s="2" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Sarah ferme le sac.
+narrateur|Ça fait zzz.
+papa|Le sac est prêt.
+maman|Bravo, Sarah.
+maman|Tu as fait du bon travail.
+papa|Tu as mis le goûter.
+maman|Et le crayon.
+papa|C'est ce que l'adulte a dit.
+enfant-f|Merci.
+narrateur|Ils restent un moment près de le palier.
+narrateur|La marche de l'escalier ne craque plus.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr"/>
@@ -2966,7 +3076,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Lila rejoint Léa. Le sol est un peu froid. On dit merci. Cette fin-là est celle de le bac à sable, le ballon et Léa. Lila a appris : Préparer son sac. Voici le geste : mettre dans le sac. Lila a entendu : sac, ce que l'adulte a dit. Lila dit merci à maman. On rentre.</t>
+          <t>Au palier, un mouchoir propre attend. Il est doux et plié. Il sent le linge. Le mouchoir dans le sac, Sarah. Le mouchoir. Sarah le pose dans une poche. Bravo. Tu as mis ce que papa a dit. Le goûter est déjà dedans. Le sac a ce que l'adulte a dit. La poche est fermée ? Oui. Le palier sent encore l'orange.</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -3106,10 +3216,26 @@
       <c r="AV12" s="2" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>narrateur|Lila rejoint Léa. Le sol est un peu froid. On dit merci. Cette fin-là est celle de le bac à sable, le ballon et Léa. Lila a appris : Préparer son sac. Voici le geste : mettre dans le sac. Lila a entendu : sac, ce que l'adulte a dit. Lila dit merci à maman. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX12" t="inlineStr"/>
+          <t>narrateur|Au palier, un mouchoir propre attend.
+narrateur|Il est doux et plié.
+narrateur|Il sent le linge.
+papa|Le mouchoir dans le sac, Sarah.
+enfant-f|Le mouchoir.
+narrateur|Sarah le pose dans une poche.
+maman|Bravo.
+maman|Tu as mis ce que papa a dit.
+narrateur|Le goûter est déjà dedans.
+papa|Le sac a ce que l'adulte a dit.
+maman|La poche est fermée ?
+enfant-f|Oui.
+narrateur|Le palier sent encore l'orange.</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>mouchoir</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3134,7 +3260,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Sarah ferme le sac. Ça fait zzz. Le sac est prêt. Bravo, Sarah. Tu as fait du bon travail. Tu as mis le goûter. Et le mouchoir. C'est ce que l'adulte a dit. Merci. Ils restent un moment près de le palier. Le palier sent encore l'orange. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -3274,7 +3400,18 @@
       <c r="AV13" s="2" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Sarah ferme le sac.
+narrateur|Ça fait zzz.
+papa|Le sac est prêt.
+maman|Bravo, Sarah.
+maman|Tu as fait du bon travail.
+papa|Tu as mis le goûter.
+maman|Et le mouchoir.
+papa|C'est ce que l'adulte a dit.
+enfant-f|Merci.
+narrateur|Ils restent un moment près de le palier.
+narrateur|Le palier sent encore l'orange.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr"/>
@@ -3302,7 +3439,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Lila rejoint Sami. Une feuille tombe. On souffle doucement. Cette fin-là est celle de le bac à sable, le ballon et Sami. Lila a appris : Préparer son sac. Voici le geste : mettre dans le sac. Lila a entendu : sac, ce que l'adulte a dit. Lila dit merci à maman. On rentre.</t>
+          <t>Au palier, un petit livre attend. Les pages sentent le papier. La couverture est lisse. Le livre dans le sac, Sarah. Le livre. Sarah le glisse à plat. Bravo. Tu as mis ce que maman a dit. Le goûter est déjà dedans. Le sac a ce que l'adulte a dit. Le livre est à plat ? Oui, papa. Le cartable jaune est un peu plus lourd.</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -3442,10 +3579,26 @@
       <c r="AV14" s="2" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>narrateur|Lila rejoint Sami. Une feuille tombe. On souffle doucement. Cette fin-là est celle de le bac à sable, le ballon et Sami. Lila a appris : Préparer son sac. Voici le geste : mettre dans le sac. Lila a entendu : sac, ce que l'adulte a dit. Lila dit merci à maman. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX14" t="inlineStr"/>
+          <t>narrateur|Au palier, un petit livre attend.
+narrateur|Les pages sentent le papier.
+narrateur|La couverture est lisse.
+maman|Le livre dans le sac, Sarah.
+enfant-f|Le livre.
+narrateur|Sarah le glisse à plat.
+papa|Bravo.
+papa|Tu as mis ce que maman a dit.
+narrateur|Le goûter est déjà dedans.
+maman|Le sac a ce que l'adulte a dit.
+papa|Le livre est à plat ?
+enfant-f|Oui, papa.
+narrateur|Le cartable jaune est un peu plus lourd.</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>livre</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3470,7 +3623,7 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Sarah ferme le sac. Ça fait zzz. Le sac est prêt. Bravo, Sarah. Tu as fait du bon travail. Tu as mis le goûter. Et le livre. C'est ce que l'adulte a dit. Merci. Ils restent un moment près de le palier. Le cartable jaune est lourd, juste ce qu'il faut. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -3610,7 +3763,18 @@
       <c r="AV15" s="2" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Sarah ferme le sac.
+narrateur|Ça fait zzz.
+papa|Le sac est prêt.
+maman|Bravo, Sarah.
+maman|Tu as fait du bon travail.
+papa|Tu as mis le goûter.
+maman|Et le livre.
+papa|C'est ce que l'adulte a dit.
+enfant-f|Merci.
+narrateur|Ils restent un moment près de le palier.
+narrateur|Le cartable jaune est lourd, juste ce qu'il faut.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr"/>
@@ -3638,7 +3802,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Lila a choisi le seau. On entend un oiseau. Le seau reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : mettre dans le sac. Lila répète tout bas : sac, ce que l'adulte a dit. On attend son tour. papa n'est pas loin.</t>
+          <t>Sarah va vers le portemanteau. Un crochet est vide, tout bas. Le bois du crochet est lisse. Le sac au crochet, Sarah. On le met comme l'adulte a dit. Sarah accroche le cartable. Le goûter reste au fond. Bravo. Tu as mis ce que papa a dit. Il tient bien ? Oui, papa. Le crochet ne bouge plus.</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -3778,10 +3942,25 @@
       <c r="AV16" s="2" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>narrateur|Lila a choisi le seau. On entend un oiseau. Le seau reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : mettre dans le sac. Lila répète tout bas : sac, ce que l'adulte a dit. On attend son tour. papa n'est pas loin.</t>
-        </is>
-      </c>
-      <c r="AX16" t="inlineStr"/>
+          <t>narrateur|Sarah va vers le portemanteau.
+narrateur|Un crochet est vide, tout bas.
+narrateur|Le bois du crochet est lisse.
+papa|Le sac au crochet, Sarah.
+papa|On le met comme l'adulte a dit.
+narrateur|Sarah accroche le cartable.
+narrateur|Le goûter reste au fond.
+maman|Bravo.
+maman|Tu as mis ce que papa a dit.
+papa|Il tient bien ?
+enfant-f|Oui, papa.
+narrateur|Le crochet ne bouge plus.</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>crochet</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3806,7 +3985,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre Tom, Léa, ou Sami.</t>
+          <t>On peut prendre le crayon, le mouchoir, ou le livre.</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -3974,7 +4153,7 @@
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
+          <t>narrateur|On peut prendre le crayon, le mouchoir, ou le livre.</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr"/>
@@ -4002,7 +4181,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>Lila rejoint Tom. Le sol est un peu froid. On range un objet. Cette fin-là est celle de le bac à sable, le seau et Tom. Lila a appris : Préparer son sac. Voici le geste : mettre dans le sac. Lila a entendu : sac, ce que l'adulte a dit. Lila dit merci à maman. On rentre.</t>
+          <t>Au portemanteau, un crayon jaune attend. Il sent le bois. La mine est bien taillée. Le crayon dans le sac, Sarah. Le crayon. Sarah le glisse près du bord. Bravo. Tu as mis ce que maman a dit. Le goûter est déjà dedans. Le sac a ce que l'adulte a dit. Tu as fini le crayon ? Oui, papa. Le crochet ne bouge plus.</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -4142,10 +4321,26 @@
       <c r="AV18" s="2" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>narrateur|Lila rejoint Tom. Le sol est un peu froid. On range un objet. Cette fin-là est celle de le bac à sable, le seau et Tom. Lila a appris : Préparer son sac. Voici le geste : mettre dans le sac. Lila a entendu : sac, ce que l'adulte a dit. Lila dit merci à maman. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX18" t="inlineStr"/>
+          <t>narrateur|Au portemanteau, un crayon jaune attend.
+narrateur|Il sent le bois.
+narrateur|La mine est bien taillée.
+maman|Le crayon dans le sac, Sarah.
+enfant-f|Le crayon.
+narrateur|Sarah le glisse près du bord.
+papa|Bravo.
+papa|Tu as mis ce que maman a dit.
+narrateur|Le goûter est déjà dedans.
+maman|Le sac a ce que l'adulte a dit.
+papa|Tu as fini le crayon ?
+enfant-f|Oui, papa.
+narrateur|Le crochet ne bouge plus.</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>crayon</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4170,7 +4365,7 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Sarah ferme le sac. Ça fait zzz. Le sac est prêt. Bravo, Sarah. Tu as fait du bon travail. Tu as mis le goûter. Et le crayon. C'est ce que l'adulte a dit. Merci. Ils restent un moment près de le portemanteau. Le crochet du portemanteau reste calme. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -4310,7 +4505,18 @@
       <c r="AV19" s="2" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Sarah ferme le sac.
+narrateur|Ça fait zzz.
+papa|Le sac est prêt.
+maman|Bravo, Sarah.
+maman|Tu as fait du bon travail.
+papa|Tu as mis le goûter.
+maman|Et le crayon.
+papa|C'est ce que l'adulte a dit.
+enfant-f|Merci.
+narrateur|Ils restent un moment près de le portemanteau.
+narrateur|Le crochet du portemanteau reste calme.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr"/>
@@ -4338,7 +4544,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>Lila rejoint Léa. Une feuille tombe. On dit merci. Cette fin-là est celle de le bac à sable, le seau et Léa. Lila a appris : Préparer son sac. Voici le geste : mettre dans le sac. Lila a entendu : sac, ce que l'adulte a dit. Lila dit merci à maman. On rentre.</t>
+          <t>Au portemanteau, un mouchoir propre attend. Il est doux et plié. Il sent le linge. Le mouchoir dans le sac, Sarah. Le mouchoir. Sarah le pose dans une poche. Bravo. Tu as mis ce que papa a dit. Le goûter est déjà dedans. Le sac a ce que l'adulte a dit. La poche est fermée ? Oui. Un manteau frôle le sac.</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -4478,10 +4684,26 @@
       <c r="AV20" s="2" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>narrateur|Lila rejoint Léa. Une feuille tombe. On dit merci. Cette fin-là est celle de le bac à sable, le seau et Léa. Lila a appris : Préparer son sac. Voici le geste : mettre dans le sac. Lila a entendu : sac, ce que l'adulte a dit. Lila dit merci à maman. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX20" t="inlineStr"/>
+          <t>narrateur|Au portemanteau, un mouchoir propre attend.
+narrateur|Il est doux et plié.
+narrateur|Il sent le linge.
+papa|Le mouchoir dans le sac, Sarah.
+enfant-f|Le mouchoir.
+narrateur|Sarah le pose dans une poche.
+maman|Bravo.
+maman|Tu as mis ce que papa a dit.
+narrateur|Le goûter est déjà dedans.
+papa|Le sac a ce que l'adulte a dit.
+maman|La poche est fermée ?
+enfant-f|Oui.
+narrateur|Un manteau frôle le sac.</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>mouchoir</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4506,7 +4728,7 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Sarah ferme le sac. Ça fait zzz. Le sac est prêt. Bravo, Sarah. Tu as fait du bon travail. Tu as mis le goûter. Et le mouchoir. C'est ce que l'adulte a dit. Merci. Ils restent un moment près de le portemanteau. Un manteau frôle encore le sac. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
@@ -4646,7 +4868,18 @@
       <c r="AV21" s="2" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Sarah ferme le sac.
+narrateur|Ça fait zzz.
+papa|Le sac est prêt.
+maman|Bravo, Sarah.
+maman|Tu as fait du bon travail.
+papa|Tu as mis le goûter.
+maman|Et le mouchoir.
+papa|C'est ce que l'adulte a dit.
+enfant-f|Merci.
+narrateur|Ils restent un moment près de le portemanteau.
+narrateur|Un manteau frôle encore le sac.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr"/>
@@ -4674,7 +4907,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>Lila rejoint Sami. L'eau coule, tout petit bruit. On souffle doucement. Cette fin-là est celle de le bac à sable, le seau et Sami. Lila a appris : Préparer son sac. Voici le geste : mettre dans le sac. Lila a entendu : sac, ce que l'adulte a dit. Lila dit merci à maman. On rentre.</t>
+          <t>Au portemanteau, un petit livre attend. Les pages sentent le papier. La couverture est lisse. Le livre dans le sac, Sarah. Le livre. Sarah le glisse à plat. Bravo. Tu as mis ce que maman a dit. Le goûter est déjà dedans. Le sac a ce que l'adulte a dit. Le livre est à plat ? Oui, papa. La boucle brille encore.</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -4814,10 +5047,26 @@
       <c r="AV22" s="2" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>narrateur|Lila rejoint Sami. L'eau coule, tout petit bruit. On souffle doucement. Cette fin-là est celle de le bac à sable, le seau et Sami. Lila a appris : Préparer son sac. Voici le geste : mettre dans le sac. Lila a entendu : sac, ce que l'adulte a dit. Lila dit merci à maman. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX22" t="inlineStr"/>
+          <t>narrateur|Au portemanteau, un petit livre attend.
+narrateur|Les pages sentent le papier.
+narrateur|La couverture est lisse.
+maman|Le livre dans le sac, Sarah.
+enfant-f|Le livre.
+narrateur|Sarah le glisse à plat.
+papa|Bravo.
+papa|Tu as mis ce que maman a dit.
+narrateur|Le goûter est déjà dedans.
+maman|Le sac a ce que l'adulte a dit.
+papa|Le livre est à plat ?
+enfant-f|Oui, papa.
+narrateur|La boucle brille encore.</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>livre</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4842,7 +5091,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Sarah ferme le sac. Ça fait zzz. Le sac est prêt. Bravo, Sarah. Tu as fait du bon travail. Tu as mis le goûter. Et le livre. C'est ce que l'adulte a dit. Merci. Ils restent un moment près de le portemanteau. La boucle du cartable est fermée. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -4982,7 +5231,18 @@
       <c r="AV23" s="2" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Sarah ferme le sac.
+narrateur|Ça fait zzz.
+papa|Le sac est prêt.
+maman|Bravo, Sarah.
+maman|Tu as fait du bon travail.
+papa|Tu as mis le goûter.
+maman|Et le livre.
+papa|C'est ce que l'adulte a dit.
+enfant-f|Merci.
+narrateur|Ils restent un moment près de le portemanteau.
+narrateur|La boucle du cartable est fermée.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr"/>
@@ -5010,7 +5270,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>Lila a choisi le doudou. Ça sent le pain chaud. Le doudou reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : mettre dans le sac. Lila répète tout bas : sac, ce que l'adulte a dit. On montre du doigt, sans courir. papa n'est pas loin.</t>
+          <t>Sarah pose le sac sur le banc. Le banc est près de la porte. La craie blanche est encore dessous. Le sac sur le banc, Sarah. Comme l'adulte a dit. Sarah pousse le cartable au milieu. Le goûter ne tombe pas. Bravo. Tu as mis ce que maman a dit. Le sac est stable ? Oui. Le soleil touche le banc.</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -5150,10 +5410,25 @@
       <c r="AV24" s="2" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>narrateur|Lila a choisi le doudou. Ça sent le pain chaud. Le doudou reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : mettre dans le sac. Lila répète tout bas : sac, ce que l'adulte a dit. On montre du doigt, sans courir. papa n'est pas loin.</t>
-        </is>
-      </c>
-      <c r="AX24" t="inlineStr"/>
+          <t>narrateur|Sarah pose le sac sur le banc.
+narrateur|Le banc est près de la porte.
+narrateur|La craie blanche est encore dessous.
+maman|Le sac sur le banc, Sarah.
+maman|Comme l'adulte a dit.
+narrateur|Sarah pousse le cartable au milieu.
+narrateur|Le goûter ne tombe pas.
+papa|Bravo.
+papa|Tu as mis ce que maman a dit.
+maman|Le sac est stable ?
+enfant-f|Oui.
+narrateur|Le soleil touche le banc.</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>banc</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5178,7 +5453,7 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre Tom, Léa, ou Sami.</t>
+          <t>On peut prendre le crayon, le mouchoir, ou le livre.</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
@@ -5346,7 +5621,7 @@
       </c>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
+          <t>narrateur|On peut prendre le crayon, le mouchoir, ou le livre.</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr"/>
@@ -5374,7 +5649,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>Lila rejoint Tom. Une feuille tombe. On range un objet. Cette fin-là est celle de le bac à sable, le doudou et Tom. Lila a appris : Préparer son sac. Voici le geste : mettre dans le sac. Lila a entendu : sac, ce que l'adulte a dit. Lila dit merci à maman. On rentre.</t>
+          <t>Sur le banc, un crayon jaune attend. Il sent le bois. La mine est bien taillée. Le crayon dans le sac, Sarah. Le crayon. Sarah le glisse près du bord. Bravo. Tu as mis ce que maman a dit. Le goûter est déjà dedans. Le sac a ce que l'adulte a dit. Tu as fini le crayon ? Oui, papa. Le soleil touche le crayon.</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -5514,10 +5789,26 @@
       <c r="AV26" s="2" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>narrateur|Lila rejoint Tom. Une feuille tombe. On range un objet. Cette fin-là est celle de le bac à sable, le doudou et Tom. Lila a appris : Préparer son sac. Voici le geste : mettre dans le sac. Lila a entendu : sac, ce que l'adulte a dit. Lila dit merci à maman. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX26" t="inlineStr"/>
+          <t>narrateur|Sur le banc, un crayon jaune attend.
+narrateur|Il sent le bois.
+narrateur|La mine est bien taillée.
+maman|Le crayon dans le sac, Sarah.
+enfant-f|Le crayon.
+narrateur|Sarah le glisse près du bord.
+papa|Bravo.
+papa|Tu as mis ce que maman a dit.
+narrateur|Le goûter est déjà dedans.
+maman|Le sac a ce que l'adulte a dit.
+papa|Tu as fini le crayon ?
+enfant-f|Oui, papa.
+narrateur|Le soleil touche le crayon.</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>crayon</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5542,7 +5833,7 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Sarah ferme le sac. Ça fait zzz. Le sac est prêt. Bravo, Sarah. Tu as fait du bon travail. Tu as mis le goûter. Et le crayon. C'est ce que l'adulte a dit. Merci. Ils restent un moment près de le banc. Le soleil a quitté le banc. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
@@ -5682,7 +5973,18 @@
       <c r="AV27" s="2" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Sarah ferme le sac.
+narrateur|Ça fait zzz.
+papa|Le sac est prêt.
+maman|Bravo, Sarah.
+maman|Tu as fait du bon travail.
+papa|Tu as mis le goûter.
+maman|Et le crayon.
+papa|C'est ce que l'adulte a dit.
+enfant-f|Merci.
+narrateur|Ils restent un moment près de le banc.
+narrateur|Le soleil a quitté le banc.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr"/>
@@ -5710,7 +6012,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>Lila rejoint Léa. L'eau coule, tout petit bruit. On dit merci. Cette fin-là est celle de le bac à sable, le doudou et Léa. Lila a appris : Préparer son sac. Voici le geste : mettre dans le sac. Lila a entendu : sac, ce que l'adulte a dit. Lila dit merci à maman. On rentre.</t>
+          <t>Sur le banc, un mouchoir propre attend. Il est doux et plié. Il sent le linge. Le mouchoir dans le sac, Sarah. Le mouchoir. Sarah le pose dans une poche. Bravo. Tu as mis ce que papa a dit. Le goûter est déjà dedans. Le sac a ce que l'adulte a dit. La poche est fermée ? Oui. La craie blanche reste sous le banc.</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -5850,10 +6152,26 @@
       <c r="AV28" s="2" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>narrateur|Lila rejoint Léa. L'eau coule, tout petit bruit. On dit merci. Cette fin-là est celle de le bac à sable, le doudou et Léa. Lila a appris : Préparer son sac. Voici le geste : mettre dans le sac. Lila a entendu : sac, ce que l'adulte a dit. Lila dit merci à maman. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX28" t="inlineStr"/>
+          <t>narrateur|Sur le banc, un mouchoir propre attend.
+narrateur|Il est doux et plié.
+narrateur|Il sent le linge.
+papa|Le mouchoir dans le sac, Sarah.
+enfant-f|Le mouchoir.
+narrateur|Sarah le pose dans une poche.
+maman|Bravo.
+maman|Tu as mis ce que papa a dit.
+narrateur|Le goûter est déjà dedans.
+papa|Le sac a ce que l'adulte a dit.
+maman|La poche est fermée ?
+enfant-f|Oui.
+narrateur|La craie blanche reste sous le banc.</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>mouchoir</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5878,7 +6196,7 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Sarah ferme le sac. Ça fait zzz. Le sac est prêt. Bravo, Sarah. Tu as fait du bon travail. Tu as mis le goûter. Et le mouchoir. C'est ce que l'adulte a dit. Merci. Ils restent un moment près de le banc. La craie blanche reste sous le banc. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
@@ -6018,7 +6336,18 @@
       <c r="AV29" s="2" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Sarah ferme le sac.
+narrateur|Ça fait zzz.
+papa|Le sac est prêt.
+maman|Bravo, Sarah.
+maman|Tu as fait du bon travail.
+papa|Tu as mis le goûter.
+maman|Et le mouchoir.
+papa|C'est ce que l'adulte a dit.
+enfant-f|Merci.
+narrateur|Ils restent un moment près de le banc.
+narrateur|La craie blanche reste sous le banc.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr"/>
@@ -6046,7 +6375,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>Lila rejoint Sami. Un vélo passe au loin. On souffle doucement. Cette fin-là est celle de le bac à sable, le doudou et Sami. Lila a appris : Préparer son sac. Voici le geste : mettre dans le sac. Lila a entendu : sac, ce que l'adulte a dit. Lila dit merci à maman. On rentre.</t>
+          <t>Sur le banc, un petit livre attend. Les pages sentent le papier. La couverture est lisse. Le livre dans le sac, Sarah. Le livre. Sarah le glisse à plat. Bravo. Tu as mis ce que maman a dit. Le goûter est déjà dedans. Le sac a ce que l'adulte a dit. Le livre est à plat ? Oui, papa. Le banc est tiède sous le sac.</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -6186,10 +6515,26 @@
       <c r="AV30" s="2" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>narrateur|Lila rejoint Sami. Un vélo passe au loin. On souffle doucement. Cette fin-là est celle de le bac à sable, le doudou et Sami. Lila a appris : Préparer son sac. Voici le geste : mettre dans le sac. Lila a entendu : sac, ce que l'adulte a dit. Lila dit merci à maman. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX30" t="inlineStr"/>
+          <t>narrateur|Sur le banc, un petit livre attend.
+narrateur|Les pages sentent le papier.
+narrateur|La couverture est lisse.
+maman|Le livre dans le sac, Sarah.
+enfant-f|Le livre.
+narrateur|Sarah le glisse à plat.
+papa|Bravo.
+papa|Tu as mis ce que maman a dit.
+narrateur|Le goûter est déjà dedans.
+maman|Le sac a ce que l'adulte a dit.
+papa|Le livre est à plat ?
+enfant-f|Oui, papa.
+narrateur|Le banc est tiède sous le sac.</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>livre</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6214,7 +6559,7 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Sarah ferme le sac. Ça fait zzz. Le sac est prêt. Bravo, Sarah. Tu as fait du bon travail. Tu as mis le goûter. Et le livre. C'est ce que l'adulte a dit. Merci. Ils restent un moment près de le banc. Le banc est vide, sauf le sac. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
@@ -6354,7 +6699,18 @@
       <c r="AV31" s="2" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Sarah ferme le sac.
+narrateur|Ça fait zzz.
+papa|Le sac est prêt.
+maman|Bravo, Sarah.
+maman|Tu as fait du bon travail.
+papa|Tu as mis le goûter.
+maman|Et le livre.
+papa|C'est ce que l'adulte a dit.
+enfant-f|Merci.
+narrateur|Ils restent un moment près de le banc.
+narrateur|Le banc est vide, sauf le sac.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr"/>
@@ -6382,7 +6738,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Lila va vers le toboggan. Les chaussures font toc toc. maman sourit. Ici, c'est le toboggan. Ce n'est pas comme les autres endroits. Lila se souvient : sac, ce que l'adulte a dit. Voici le geste : mettre dans le sac. On dit merci. Je suis là. On reste ensemble.</t>
+          <t>Le cahier bleu est sur la marche. Les pages sentent le papier. Un coin est un peu plié. Le cahier dans le sac, Sarah. Le cahier. Sarah le glisse à plat. Le cahier rentre tout seul. Bravo. Tu as mis ce que papa a dit. Tu as fini de mettre le cahier ? Oui, papa. La boucle brille encore. Le sac a ce que l'adulte a dit.</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -6522,11 +6878,26 @@
       <c r="AV32" s="2" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>narrateur|Lila va vers le toboggan. Les chaussures font toc toc. maman sourit. Ici, c'est le toboggan. Ce n'est pas comme les autres endroits. Lila se souvient : sac, ce que l'adulte a dit. Voici le geste : mettre dans le sac. On dit merci.
-maman|Je suis là. On reste ensemble.</t>
-        </is>
-      </c>
-      <c r="AX32" t="inlineStr"/>
+          <t>narrateur|Le cahier bleu est sur la marche.
+narrateur|Les pages sentent le papier.
+narrateur|Un coin est un peu plié.
+papa|Le cahier dans le sac, Sarah.
+enfant-f|Le cahier.
+narrateur|Sarah le glisse à plat.
+narrateur|Le cahier rentre tout seul.
+maman|Bravo.
+maman|Tu as mis ce que papa a dit.
+papa|Tu as fini de mettre le cahier ?
+enfant-f|Oui, papa.
+narrateur|La boucle brille encore.
+maman|Le sac a ce que l'adulte a dit.</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>cahier</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6551,7 +6922,7 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>Que fait-on ? Préparer son sac.</t>
+          <t>On met ce que l'adulte a dit ?</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
@@ -6711,7 +7082,7 @@
       </c>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>narrateur|Que fait-on ? Préparer son sac.</t>
+          <t>narrateur|On met ce que l'adulte a dit ?</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr"/>
@@ -6739,7 +7110,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>Oui. Voici le geste : mettre dans le sac. Lila respire. Lila retient : sac, ce que l'adulte a dit. On continue, avec maman.</t>
+          <t>Oui. On met dans le sac ce que maman a dit. Ou ce que papa a dit. Bravo, Sarah. Tu as écouté. C'est du bon travail. Le sac a ce que l'adulte a dit. Le cahier est dedans. On continue ensemble ? Oui.</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -6883,7 +7254,16 @@
       </c>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>narrateur|Oui. Voici le geste : mettre dans le sac. Lila respire. Lila retient : sac, ce que l'adulte a dit. On continue, avec maman.</t>
+          <t>narrateur|Oui.
+narrateur|On met dans le sac ce que maman a dit.
+narrateur|Ou ce que papa a dit.
+maman|Bravo, Sarah.
+maman|Tu as écouté.
+papa|C'est du bon travail.
+papa|Le sac a ce que l'adulte a dit.
+enfant-f|Le cahier est dedans.
+maman|On continue ensemble ?
+enfant-f|Oui.</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr"/>
@@ -6911,7 +7291,7 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le ballon, le seau, ou le doudou.</t>
+          <t>On peut aller au palier, au portemanteau, ou au banc.</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
@@ -7075,7 +7455,7 @@
       <c r="AV35" s="2" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le ballon, le seau, ou le doudou.</t>
+          <t>narrateur|On peut aller au palier, au portemanteau, ou au banc.</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr"/>
@@ -7103,7 +7483,7 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>Lila a choisi le ballon. Le vent est doux. Le ballon reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : mettre dans le sac. Lila répète tout bas : sac, ce que l'adulte a dit. On écoute jusqu'au bout. papa n'est pas loin.</t>
+          <t>Sarah porte le cahier au palier. Le sac est déjà sur la marche. La boucle est un peu ouverte. Le cahier reste dans le sac. C'est ce que l'adulte a dit. Sarah appuie un peu. Le cahier est à plat. Bravo. Tu as mis ce que papa a dit. Tu as fini au palier ? Oui, papa. L'escalier sent le bois.</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -7243,10 +7623,25 @@
       <c r="AV36" s="2" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>narrateur|Lila a choisi le ballon. Le vent est doux. Le ballon reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : mettre dans le sac. Lila répète tout bas : sac, ce que l'adulte a dit. On écoute jusqu'au bout. papa n'est pas loin.</t>
-        </is>
-      </c>
-      <c r="AX36" t="inlineStr"/>
+          <t>narrateur|Sarah porte le cahier au palier.
+narrateur|Le sac est déjà sur la marche.
+narrateur|La boucle est un peu ouverte.
+papa|Le cahier reste dans le sac.
+papa|C'est ce que l'adulte a dit.
+narrateur|Sarah appuie un peu.
+narrateur|Le cahier est à plat.
+maman|Bravo.
+maman|Tu as mis ce que papa a dit.
+papa|Tu as fini au palier ?
+enfant-f|Oui, papa.
+narrateur|L'escalier sent le bois.</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>escalier</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7271,7 +7666,7 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre Tom, Léa, ou Sami.</t>
+          <t>On peut prendre le crayon, le mouchoir, ou le livre.</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
@@ -7439,7 +7834,7 @@
       </c>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
+          <t>narrateur|On peut prendre le crayon, le mouchoir, ou le livre.</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr"/>
@@ -7467,7 +7862,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>Lila rejoint Tom. Le sol est un peu froid. On dit merci. Cette fin-là est celle de le toboggan, le ballon et Tom. Lila a appris : Préparer son sac. Voici le geste : mettre dans le sac. Lila a entendu : sac, ce que l'adulte a dit. Lila dit merci à maman. On rentre.</t>
+          <t>Au palier, un crayon jaune attend. Il sent le bois. La mine est bien taillée. Le crayon dans le sac, Sarah. Le crayon. Sarah le glisse près du bord. Bravo. Tu as mis ce que maman a dit. Le cahier est déjà dedans. Le sac a ce que l'adulte a dit. Tu as fini le crayon ? Oui, papa. Le cahier bleu ne glisse pas.</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -7607,10 +8002,26 @@
       <c r="AV38" s="2" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>narrateur|Lila rejoint Tom. Le sol est un peu froid. On dit merci. Cette fin-là est celle de le toboggan, le ballon et Tom. Lila a appris : Préparer son sac. Voici le geste : mettre dans le sac. Lila a entendu : sac, ce que l'adulte a dit. Lila dit merci à maman. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX38" t="inlineStr"/>
+          <t>narrateur|Au palier, un crayon jaune attend.
+narrateur|Il sent le bois.
+narrateur|La mine est bien taillée.
+maman|Le crayon dans le sac, Sarah.
+enfant-f|Le crayon.
+narrateur|Sarah le glisse près du bord.
+papa|Bravo.
+papa|Tu as mis ce que maman a dit.
+narrateur|Le cahier est déjà dedans.
+maman|Le sac a ce que l'adulte a dit.
+papa|Tu as fini le crayon ?
+enfant-f|Oui, papa.
+narrateur|Le cahier bleu ne glisse pas.</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>crayon</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7635,7 +8046,7 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Sarah ferme le sac. Ça fait zzz. Le sac est prêt. Bravo, Sarah. Tu as fait du bon travail. Tu as mis le cahier. Et le crayon. C'est ce que l'adulte a dit. Merci. Ils restent un moment près de le palier. Le cahier bleu ne bouge plus. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
@@ -7775,7 +8186,18 @@
       <c r="AV39" s="2" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Sarah ferme le sac.
+narrateur|Ça fait zzz.
+papa|Le sac est prêt.
+maman|Bravo, Sarah.
+maman|Tu as fait du bon travail.
+papa|Tu as mis le cahier.
+maman|Et le crayon.
+papa|C'est ce que l'adulte a dit.
+enfant-f|Merci.
+narrateur|Ils restent un moment près de le palier.
+narrateur|Le cahier bleu ne bouge plus.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr"/>
@@ -7803,7 +8225,7 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>Lila rejoint Léa. Une feuille tombe. On souffle doucement. Cette fin-là est celle de le toboggan, le ballon et Léa. Lila a appris : Préparer son sac. Voici le geste : mettre dans le sac. Lila a entendu : sac, ce que l'adulte a dit. Lila dit merci à maman. On rentre.</t>
+          <t>Au palier, un mouchoir propre attend. Il est doux et plié. Il sent le linge. Le mouchoir dans le sac, Sarah. Le mouchoir. Sarah le pose dans une poche. Bravo. Tu as mis ce que papa a dit. Le cahier est déjà dedans. Le sac a ce que l'adulte a dit. La poche est fermée ? Oui. L'escalier sent le bois.</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
@@ -7943,10 +8365,26 @@
       <c r="AV40" s="2" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>narrateur|Lila rejoint Léa. Une feuille tombe. On souffle doucement. Cette fin-là est celle de le toboggan, le ballon et Léa. Lila a appris : Préparer son sac. Voici le geste : mettre dans le sac. Lila a entendu : sac, ce que l'adulte a dit. Lila dit merci à maman. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX40" t="inlineStr"/>
+          <t>narrateur|Au palier, un mouchoir propre attend.
+narrateur|Il est doux et plié.
+narrateur|Il sent le linge.
+papa|Le mouchoir dans le sac, Sarah.
+enfant-f|Le mouchoir.
+narrateur|Sarah le pose dans une poche.
+maman|Bravo.
+maman|Tu as mis ce que papa a dit.
+narrateur|Le cahier est déjà dedans.
+papa|Le sac a ce que l'adulte a dit.
+maman|La poche est fermée ?
+enfant-f|Oui.
+narrateur|L'escalier sent le bois.</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>mouchoir</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -7971,7 +8409,7 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Sarah ferme le sac. Ça fait zzz. Le sac est prêt. Bravo, Sarah. Tu as fait du bon travail. Tu as mis le cahier. Et le mouchoir. C'est ce que l'adulte a dit. Merci. Ils restent un moment près de le palier. L'escalier sent le bois et le papier. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
@@ -8111,7 +8549,18 @@
       <c r="AV41" s="2" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Sarah ferme le sac.
+narrateur|Ça fait zzz.
+papa|Le sac est prêt.
+maman|Bravo, Sarah.
+maman|Tu as fait du bon travail.
+papa|Tu as mis le cahier.
+maman|Et le mouchoir.
+papa|C'est ce que l'adulte a dit.
+enfant-f|Merci.
+narrateur|Ils restent un moment près de le palier.
+narrateur|L'escalier sent le bois et le papier.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr"/>
@@ -8139,7 +8588,7 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>Lila rejoint Sami. L'eau coule, tout petit bruit. On écoute jusqu'au bout. Cette fin-là est celle de le toboggan, le ballon et Sami. Lila a appris : Préparer son sac. Voici le geste : mettre dans le sac. Lila a entendu : sac, ce que l'adulte a dit. Lila dit merci à maman. On rentre.</t>
+          <t>Au palier, un petit livre attend. Les pages sentent le papier. La couverture est lisse. Le livre dans le sac, Sarah. Le livre. Sarah le glisse à plat. Bravo. Tu as mis ce que maman a dit. Le cahier est déjà dedans. Le sac a ce que l'adulte a dit. Le livre est à plat ? Oui, papa. Sarah appuie un peu le rabat.</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
@@ -8279,10 +8728,26 @@
       <c r="AV42" s="2" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>narrateur|Lila rejoint Sami. L'eau coule, tout petit bruit. On écoute jusqu'au bout. Cette fin-là est celle de le toboggan, le ballon et Sami. Lila a appris : Préparer son sac. Voici le geste : mettre dans le sac. Lila a entendu : sac, ce que l'adulte a dit. Lila dit merci à maman. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX42" t="inlineStr"/>
+          <t>narrateur|Au palier, un petit livre attend.
+narrateur|Les pages sentent le papier.
+narrateur|La couverture est lisse.
+maman|Le livre dans le sac, Sarah.
+enfant-f|Le livre.
+narrateur|Sarah le glisse à plat.
+papa|Bravo.
+papa|Tu as mis ce que maman a dit.
+narrateur|Le cahier est déjà dedans.
+maman|Le sac a ce que l'adulte a dit.
+papa|Le livre est à plat ?
+enfant-f|Oui, papa.
+narrateur|Sarah appuie un peu le rabat.</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>livre</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8307,7 +8772,7 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Sarah ferme le sac. Ça fait zzz. Le sac est prêt. Bravo, Sarah. Tu as fait du bon travail. Tu as mis le cahier. Et le livre. C'est ce que l'adulte a dit. Merci. Ils restent un moment près de le palier. Sarah appuie une dernière fois sur le rabat. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
@@ -8447,7 +8912,18 @@
       <c r="AV43" s="2" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Sarah ferme le sac.
+narrateur|Ça fait zzz.
+papa|Le sac est prêt.
+maman|Bravo, Sarah.
+maman|Tu as fait du bon travail.
+papa|Tu as mis le cahier.
+maman|Et le livre.
+papa|C'est ce que l'adulte a dit.
+enfant-f|Merci.
+narrateur|Ils restent un moment près de le palier.
+narrateur|Sarah appuie une dernière fois sur le rabat.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr"/>
@@ -8475,7 +8951,7 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>Lila a choisi le seau. Le sol est un peu froid. Le seau reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : mettre dans le sac. Lila répète tout bas : sac, ce que l'adulte a dit. On attend son tour. papa n'est pas loin.</t>
+          <t>Sarah accroche le sac au portemanteau. Le cahier pèse un peu. Le crochet fait un petit clic. Le cahier dans le sac. Comme l'adulte a dit. Sarah vérifie la boucle. Le cahier ne glisse pas. Bravo. Tu as mis ce que maman a dit. Le crochet est bon ? Oui, maman. Un manteau voisin frôle le sac.</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
@@ -8615,10 +9091,25 @@
       <c r="AV44" s="2" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>narrateur|Lila a choisi le seau. Le sol est un peu froid. Le seau reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : mettre dans le sac. Lila répète tout bas : sac, ce que l'adulte a dit. On attend son tour. papa n'est pas loin.</t>
-        </is>
-      </c>
-      <c r="AX44" t="inlineStr"/>
+          <t>narrateur|Sarah accroche le sac au portemanteau.
+narrateur|Le cahier pèse un peu.
+narrateur|Le crochet fait un petit clic.
+maman|Le cahier dans le sac.
+maman|Comme l'adulte a dit.
+narrateur|Sarah vérifie la boucle.
+narrateur|Le cahier ne glisse pas.
+papa|Bravo.
+papa|Tu as mis ce que maman a dit.
+maman|Le crochet est bon ?
+enfant-f|Oui, maman.
+narrateur|Un manteau voisin frôle le sac.</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>crochet</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8643,7 +9134,7 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre Tom, Léa, ou Sami.</t>
+          <t>On peut prendre le crayon, le mouchoir, ou le livre.</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
@@ -8811,7 +9302,7 @@
       </c>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
+          <t>narrateur|On peut prendre le crayon, le mouchoir, ou le livre.</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr"/>
@@ -8839,7 +9330,7 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>Lila rejoint Tom. Une feuille tombe. On dit merci. Cette fin-là est celle de le toboggan, le seau et Tom. Lila a appris : Préparer son sac. Voici le geste : mettre dans le sac. Lila a entendu : sac, ce que l'adulte a dit. Lila dit merci à maman. On rentre.</t>
+          <t>Au portemanteau, un crayon jaune attend. Il sent le bois. La mine est bien taillée. Le crayon dans le sac, Sarah. Le crayon. Sarah le glisse près du bord. Bravo. Tu as mis ce que maman a dit. Le cahier est déjà dedans. Le sac a ce que l'adulte a dit. Tu as fini le crayon ? Oui, papa. Le portemanteau fait clic.</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
@@ -8979,10 +9470,26 @@
       <c r="AV46" s="2" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>narrateur|Lila rejoint Tom. Une feuille tombe. On dit merci. Cette fin-là est celle de le toboggan, le seau et Tom. Lila a appris : Préparer son sac. Voici le geste : mettre dans le sac. Lila a entendu : sac, ce que l'adulte a dit. Lila dit merci à maman. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX46" t="inlineStr"/>
+          <t>narrateur|Au portemanteau, un crayon jaune attend.
+narrateur|Il sent le bois.
+narrateur|La mine est bien taillée.
+maman|Le crayon dans le sac, Sarah.
+enfant-f|Le crayon.
+narrateur|Sarah le glisse près du bord.
+papa|Bravo.
+papa|Tu as mis ce que maman a dit.
+narrateur|Le cahier est déjà dedans.
+maman|Le sac a ce que l'adulte a dit.
+papa|Tu as fini le crayon ?
+enfant-f|Oui, papa.
+narrateur|Le portemanteau fait clic.</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>crayon</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -9007,7 +9514,7 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Sarah ferme le sac. Ça fait zzz. Le sac est prêt. Bravo, Sarah. Tu as fait du bon travail. Tu as mis le cahier. Et le crayon. C'est ce que l'adulte a dit. Merci. Ils restent un moment près de le portemanteau. Le portemanteau fait un tout petit clic. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
@@ -9147,7 +9654,18 @@
       <c r="AV47" s="2" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Sarah ferme le sac.
+narrateur|Ça fait zzz.
+papa|Le sac est prêt.
+maman|Bravo, Sarah.
+maman|Tu as fait du bon travail.
+papa|Tu as mis le cahier.
+maman|Et le crayon.
+papa|C'est ce que l'adulte a dit.
+enfant-f|Merci.
+narrateur|Ils restent un moment près de le portemanteau.
+narrateur|Le portemanteau fait un tout petit clic.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr"/>
@@ -9175,7 +9693,7 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>Lila rejoint Léa. L'eau coule, tout petit bruit. On souffle doucement. Cette fin-là est celle de le toboggan, le seau et Léa. Lila a appris : Préparer son sac. Voici le geste : mettre dans le sac. Lila a entendu : sac, ce que l'adulte a dit. Lila dit merci à maman. On rentre.</t>
+          <t>Au portemanteau, un mouchoir propre attend. Il est doux et plié. Il sent le linge. Le mouchoir dans le sac, Sarah. Le mouchoir. Sarah le pose dans une poche. Bravo. Tu as mis ce que papa a dit. Le cahier est déjà dedans. Le sac a ce que l'adulte a dit. La poche est fermée ? Oui. Le crochet tient bien.</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
@@ -9315,10 +9833,26 @@
       <c r="AV48" s="2" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>narrateur|Lila rejoint Léa. L'eau coule, tout petit bruit. On souffle doucement. Cette fin-là est celle de le toboggan, le seau et Léa. Lila a appris : Préparer son sac. Voici le geste : mettre dans le sac. Lila a entendu : sac, ce que l'adulte a dit. Lila dit merci à maman. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX48" t="inlineStr"/>
+          <t>narrateur|Au portemanteau, un mouchoir propre attend.
+narrateur|Il est doux et plié.
+narrateur|Il sent le linge.
+papa|Le mouchoir dans le sac, Sarah.
+enfant-f|Le mouchoir.
+narrateur|Sarah le pose dans une poche.
+maman|Bravo.
+maman|Tu as mis ce que papa a dit.
+narrateur|Le cahier est déjà dedans.
+papa|Le sac a ce que l'adulte a dit.
+maman|La poche est fermée ?
+enfant-f|Oui.
+narrateur|Le crochet tient bien.</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>mouchoir</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9343,7 +9877,7 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Sarah ferme le sac. Ça fait zzz. Le sac est prêt. Bravo, Sarah. Tu as fait du bon travail. Tu as mis le cahier. Et le mouchoir. C'est ce que l'adulte a dit. Merci. Ils restent un moment près de le portemanteau. Le crochet tient le cahier et le mouchoir. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
@@ -9483,7 +10017,18 @@
       <c r="AV49" s="2" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Sarah ferme le sac.
+narrateur|Ça fait zzz.
+papa|Le sac est prêt.
+maman|Bravo, Sarah.
+maman|Tu as fait du bon travail.
+papa|Tu as mis le cahier.
+maman|Et le mouchoir.
+papa|C'est ce que l'adulte a dit.
+enfant-f|Merci.
+narrateur|Ils restent un moment près de le portemanteau.
+narrateur|Le crochet tient le cahier et le mouchoir.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr"/>
@@ -9511,7 +10056,7 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>Lila rejoint Sami. Un vélo passe au loin. On écoute jusqu'au bout. Cette fin-là est celle de le toboggan, le seau et Sami. Lila a appris : Préparer son sac. Voici le geste : mettre dans le sac. Lila a entendu : sac, ce que l'adulte a dit. Lila dit merci à maman. On rentre.</t>
+          <t>Au portemanteau, un petit livre attend. Les pages sentent le papier. La couverture est lisse. Le livre dans le sac, Sarah. Le livre. Sarah le glisse à plat. Bravo. Tu as mis ce que maman a dit. Le cahier est déjà dedans. Le sac a ce que l'adulte a dit. Le livre est à plat ? Oui, papa. Le sac pend tout droit.</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
@@ -9651,10 +10196,26 @@
       <c r="AV50" s="2" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>narrateur|Lila rejoint Sami. Un vélo passe au loin. On écoute jusqu'au bout. Cette fin-là est celle de le toboggan, le seau et Sami. Lila a appris : Préparer son sac. Voici le geste : mettre dans le sac. Lila a entendu : sac, ce que l'adulte a dit. Lila dit merci à maman. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX50" t="inlineStr"/>
+          <t>narrateur|Au portemanteau, un petit livre attend.
+narrateur|Les pages sentent le papier.
+narrateur|La couverture est lisse.
+maman|Le livre dans le sac, Sarah.
+enfant-f|Le livre.
+narrateur|Sarah le glisse à plat.
+papa|Bravo.
+papa|Tu as mis ce que maman a dit.
+narrateur|Le cahier est déjà dedans.
+maman|Le sac a ce que l'adulte a dit.
+papa|Le livre est à plat ?
+enfant-f|Oui, papa.
+narrateur|Le sac pend tout droit.</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>livre</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9679,7 +10240,7 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Sarah ferme le sac. Ça fait zzz. Le sac est prêt. Bravo, Sarah. Tu as fait du bon travail. Tu as mis le cahier. Et le livre. C'est ce que l'adulte a dit. Merci. Ils restent un moment près de le portemanteau. Le sac pend droit, tout sage. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
@@ -9819,7 +10380,18 @@
       <c r="AV51" s="2" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Sarah ferme le sac.
+narrateur|Ça fait zzz.
+papa|Le sac est prêt.
+maman|Bravo, Sarah.
+maman|Tu as fait du bon travail.
+papa|Tu as mis le cahier.
+maman|Et le livre.
+papa|C'est ce que l'adulte a dit.
+enfant-f|Merci.
+narrateur|Ils restent un moment près de le portemanteau.
+narrateur|Le sac pend droit, tout sage.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr"/>
@@ -9847,7 +10419,7 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>Lila a choisi le doudou. Une feuille tombe. Le doudou reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : mettre dans le sac. Lila répète tout bas : sac, ce que l'adulte a dit. On montre du doigt, sans courir. papa n'est pas loin.</t>
+          <t>Sarah pose le sac sur le banc. Le cahier bleu se voit un peu. Le bois du banc est lisse. Le cahier reste dans le sac. C'est ce que l'adulte a dit. Sarah appuie le rabat. Le cahier est bien. Bravo. Tu as mis ce que papa a dit. Le banc est calme ? Oui. La craie reste sous le banc.</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
@@ -9987,10 +10559,25 @@
       <c r="AV52" s="2" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>narrateur|Lila a choisi le doudou. Une feuille tombe. Le doudou reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : mettre dans le sac. Lila répète tout bas : sac, ce que l'adulte a dit. On montre du doigt, sans courir. papa n'est pas loin.</t>
-        </is>
-      </c>
-      <c r="AX52" t="inlineStr"/>
+          <t>narrateur|Sarah pose le sac sur le banc.
+narrateur|Le cahier bleu se voit un peu.
+narrateur|Le bois du banc est lisse.
+papa|Le cahier reste dans le sac.
+papa|C'est ce que l'adulte a dit.
+narrateur|Sarah appuie le rabat.
+narrateur|Le cahier est bien.
+maman|Bravo.
+maman|Tu as mis ce que papa a dit.
+papa|Le banc est calme ?
+enfant-f|Oui.
+narrateur|La craie reste sous le banc.</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>banc</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -10015,7 +10602,7 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre Tom, Léa, ou Sami.</t>
+          <t>On peut prendre le crayon, le mouchoir, ou le livre.</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
@@ -10183,7 +10770,7 @@
       </c>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
+          <t>narrateur|On peut prendre le crayon, le mouchoir, ou le livre.</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr"/>
@@ -10211,7 +10798,7 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>Lila rejoint Tom. L'eau coule, tout petit bruit. On dit merci. Cette fin-là est celle de le toboggan, le doudou et Tom. Lila a appris : Préparer son sac. Voici le geste : mettre dans le sac. Lila a entendu : sac, ce que l'adulte a dit. Lila dit merci à maman. On rentre.</t>
+          <t>Sur le banc, un crayon jaune attend. Il sent le bois. La mine est bien taillée. Le crayon dans le sac, Sarah. Le crayon. Sarah le glisse près du bord. Bravo. Tu as mis ce que maman a dit. Le cahier est déjà dedans. Le sac a ce que l'adulte a dit. Tu as fini le crayon ? Oui, papa. Le banc est lisse.</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
@@ -10351,10 +10938,26 @@
       <c r="AV54" s="2" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>narrateur|Lila rejoint Tom. L'eau coule, tout petit bruit. On dit merci. Cette fin-là est celle de le toboggan, le doudou et Tom. Lila a appris : Préparer son sac. Voici le geste : mettre dans le sac. Lila a entendu : sac, ce que l'adulte a dit. Lila dit merci à maman. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX54" t="inlineStr"/>
+          <t>narrateur|Sur le banc, un crayon jaune attend.
+narrateur|Il sent le bois.
+narrateur|La mine est bien taillée.
+maman|Le crayon dans le sac, Sarah.
+enfant-f|Le crayon.
+narrateur|Sarah le glisse près du bord.
+papa|Bravo.
+papa|Tu as mis ce que maman a dit.
+narrateur|Le cahier est déjà dedans.
+maman|Le sac a ce que l'adulte a dit.
+papa|Tu as fini le crayon ?
+enfant-f|Oui, papa.
+narrateur|Le banc est lisse.</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>crayon</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10379,7 +10982,7 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Sarah ferme le sac. Ça fait zzz. Le sac est prêt. Bravo, Sarah. Tu as fait du bon travail. Tu as mis le cahier. Et le crayon. C'est ce que l'adulte a dit. Merci. Ils restent un moment près de le banc. Le banc est lisse sous le cartable. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
@@ -10519,7 +11122,18 @@
       <c r="AV55" s="2" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Sarah ferme le sac.
+narrateur|Ça fait zzz.
+papa|Le sac est prêt.
+maman|Bravo, Sarah.
+maman|Tu as fait du bon travail.
+papa|Tu as mis le cahier.
+maman|Et le crayon.
+papa|C'est ce que l'adulte a dit.
+enfant-f|Merci.
+narrateur|Ils restent un moment près de le banc.
+narrateur|Le banc est lisse sous le cartable.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr"/>
@@ -10547,7 +11161,7 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>Lila rejoint Léa. Un vélo passe au loin. On souffle doucement. Cette fin-là est celle de le toboggan, le doudou et Léa. Lila a appris : Préparer son sac. Voici le geste : mettre dans le sac. Lila a entendu : sac, ce que l'adulte a dit. Lila dit merci à maman. On rentre.</t>
+          <t>Sur le banc, un mouchoir propre attend. Il est doux et plié. Il sent le linge. Le mouchoir dans le sac, Sarah. Le mouchoir. Sarah le pose dans une poche. Bravo. Tu as mis ce que papa a dit. Le cahier est déjà dedans. Le sac a ce que l'adulte a dit. La poche est fermée ? Oui. Une poussière de craie brille.</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
@@ -10687,10 +11301,26 @@
       <c r="AV56" s="2" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>narrateur|Lila rejoint Léa. Un vélo passe au loin. On souffle doucement. Cette fin-là est celle de le toboggan, le doudou et Léa. Lila a appris : Préparer son sac. Voici le geste : mettre dans le sac. Lila a entendu : sac, ce que l'adulte a dit. Lila dit merci à maman. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX56" t="inlineStr"/>
+          <t>narrateur|Sur le banc, un mouchoir propre attend.
+narrateur|Il est doux et plié.
+narrateur|Il sent le linge.
+papa|Le mouchoir dans le sac, Sarah.
+enfant-f|Le mouchoir.
+narrateur|Sarah le pose dans une poche.
+maman|Bravo.
+maman|Tu as mis ce que papa a dit.
+narrateur|Le cahier est déjà dedans.
+papa|Le sac a ce que l'adulte a dit.
+maman|La poche est fermée ?
+enfant-f|Oui.
+narrateur|Une poussière de craie brille.</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>mouchoir</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10715,7 +11345,7 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Sarah ferme le sac. Ça fait zzz. Le sac est prêt. Bravo, Sarah. Tu as fait du bon travail. Tu as mis le cahier. Et le mouchoir. C'est ce que l'adulte a dit. Merci. Ils restent un moment près de le banc. Une poussière de craie brille. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
@@ -10855,7 +11485,18 @@
       <c r="AV57" s="2" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Sarah ferme le sac.
+narrateur|Ça fait zzz.
+papa|Le sac est prêt.
+maman|Bravo, Sarah.
+maman|Tu as fait du bon travail.
+papa|Tu as mis le cahier.
+maman|Et le mouchoir.
+papa|C'est ce que l'adulte a dit.
+enfant-f|Merci.
+narrateur|Ils restent un moment près de le banc.
+narrateur|Une poussière de craie brille.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr"/>
@@ -10883,7 +11524,7 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>Lila rejoint Sami. La lumière est claire. On écoute jusqu'au bout. Cette fin-là est celle de le toboggan, le doudou et Sami. Lila a appris : Préparer son sac. Voici le geste : mettre dans le sac. Lila a entendu : sac, ce que l'adulte a dit. Lila dit merci à maman. On rentre.</t>
+          <t>Sur le banc, un petit livre attend. Les pages sentent le papier. La couverture est lisse. Le livre dans le sac, Sarah. Le livre. Sarah le glisse à plat. Bravo. Tu as mis ce que maman a dit. Le cahier est déjà dedans. Le sac a ce que l'adulte a dit. Le livre est à plat ? Oui, papa. Le livre est tout au fond.</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
@@ -11023,10 +11664,26 @@
       <c r="AV58" s="2" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>narrateur|Lila rejoint Sami. La lumière est claire. On écoute jusqu'au bout. Cette fin-là est celle de le toboggan, le doudou et Sami. Lila a appris : Préparer son sac. Voici le geste : mettre dans le sac. Lila a entendu : sac, ce que l'adulte a dit. Lila dit merci à maman. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX58" t="inlineStr"/>
+          <t>narrateur|Sur le banc, un petit livre attend.
+narrateur|Les pages sentent le papier.
+narrateur|La couverture est lisse.
+maman|Le livre dans le sac, Sarah.
+enfant-f|Le livre.
+narrateur|Sarah le glisse à plat.
+papa|Bravo.
+papa|Tu as mis ce que maman a dit.
+narrateur|Le cahier est déjà dedans.
+maman|Le sac a ce que l'adulte a dit.
+papa|Le livre est à plat ?
+enfant-f|Oui, papa.
+narrateur|Le livre est tout au fond.</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>livre</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -11051,7 +11708,7 @@
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Sarah ferme le sac. Ça fait zzz. Le sac est prêt. Bravo, Sarah. Tu as fait du bon travail. Tu as mis le cahier. Et le livre. C'est ce que l'adulte a dit. Merci. Ils restent un moment près de le banc. Le livre est à plat, tout au fond. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
@@ -11191,7 +11848,18 @@
       <c r="AV59" s="2" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Sarah ferme le sac.
+narrateur|Ça fait zzz.
+papa|Le sac est prêt.
+maman|Bravo, Sarah.
+maman|Tu as fait du bon travail.
+papa|Tu as mis le cahier.
+maman|Et le livre.
+papa|C'est ce que l'adulte a dit.
+enfant-f|Merci.
+narrateur|Ils restent un moment près de le banc.
+narrateur|Le livre est à plat, tout au fond.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr"/>
@@ -11219,7 +11887,7 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>Lila va vers les balançoires. La couverture est douce. maman sourit. Ici, c'est les balançoires. Ce n'est pas comme les autres endroits. Lila se souvient : sac, ce que l'adulte a dit. Voici le geste : mettre dans le sac. On souffle doucement. Je suis là. On reste ensemble.</t>
+          <t>La gourde est près de la peau d'orange. Elle est froide et lisse. Le bouchon fait clic. La gourde dans le sac, Sarah. La gourde. Sarah la pose tout doux. La gourde touche le fond. Bravo. Tu as mis ce que maman a dit. Tu as fini de mettre la gourde ? Oui. Une goutte perle sur le bouchon. Le sac a ce que l'adulte a dit.</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
@@ -11359,11 +12027,26 @@
       <c r="AV60" s="2" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>narrateur|Lila va vers les balançoires. La couverture est douce. maman sourit. Ici, c'est les balançoires. Ce n'est pas comme les autres endroits. Lila se souvient : sac, ce que l'adulte a dit. Voici le geste : mettre dans le sac. On souffle doucement.
-maman|Je suis là. On reste ensemble.</t>
-        </is>
-      </c>
-      <c r="AX60" t="inlineStr"/>
+          <t>narrateur|La gourde est près de la peau d'orange.
+narrateur|Elle est froide et lisse.
+narrateur|Le bouchon fait clic.
+maman|La gourde dans le sac, Sarah.
+enfant-f|La gourde.
+narrateur|Sarah la pose tout doux.
+narrateur|La gourde touche le fond.
+papa|Bravo.
+papa|Tu as mis ce que maman a dit.
+maman|Tu as fini de mettre la gourde ?
+enfant-f|Oui.
+narrateur|Une goutte perle sur le bouchon.
+papa|Le sac a ce que l'adulte a dit.</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>gourde</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11388,7 +12071,7 @@
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>Que fait-on ? Préparer son sac.</t>
+          <t>Qui dit ce qu'on met ?</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
@@ -11548,7 +12231,7 @@
       </c>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>narrateur|Que fait-on ? Préparer son sac.</t>
+          <t>narrateur|Qui dit ce qu'on met ?</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr"/>
@@ -11576,7 +12259,7 @@
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>Oui. Voici le geste : mettre dans le sac. Lila respire. Lila retient : sac, ce que l'adulte a dit. On continue, avec maman.</t>
+          <t>Oui. On met dans le sac ce que maman a dit. Ou ce que papa a dit. Bravo, Sarah. Tu as écouté. C'est du bon travail. Le sac a ce que l'adulte a dit. La gourde est dedans. On continue ensemble ? Oui.</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
@@ -11720,7 +12403,16 @@
       </c>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>narrateur|Oui. Voici le geste : mettre dans le sac. Lila respire. Lila retient : sac, ce que l'adulte a dit. On continue, avec maman.</t>
+          <t>narrateur|Oui.
+narrateur|On met dans le sac ce que maman a dit.
+narrateur|Ou ce que papa a dit.
+maman|Bravo, Sarah.
+maman|Tu as écouté.
+papa|C'est du bon travail.
+papa|Le sac a ce que l'adulte a dit.
+enfant-f|La gourde est dedans.
+maman|On continue ensemble ?
+enfant-f|Oui.</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr"/>
@@ -11748,7 +12440,7 @@
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le ballon, le seau, ou le doudou.</t>
+          <t>On peut aller au palier, au portemanteau, ou au banc.</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
@@ -11912,7 +12604,7 @@
       <c r="AV63" s="2" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le ballon, le seau, ou le doudou.</t>
+          <t>narrateur|On peut aller au palier, au portemanteau, ou au banc.</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr"/>
@@ -11940,7 +12632,7 @@
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>Lila a choisi le ballon. L'eau coule, tout petit bruit. Le ballon reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : mettre dans le sac. Lila répète tout bas : sac, ce que l'adulte a dit. On écoute jusqu'au bout. papa n'est pas loin.</t>
+          <t>Sarah monte la gourde au palier. La gourde cliquette dans le sac. La marche craque, tout doux. La gourde dans le sac, Sarah. Comme l'adulte a dit. Sarah pose le cartable. La gourde reste droite. Bravo. Tu as mis ce que maman a dit. Elle ne tombe pas ? Non. L'orange sent encore en bas.</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
@@ -12080,10 +12772,25 @@
       <c r="AV64" s="2" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>narrateur|Lila a choisi le ballon. L'eau coule, tout petit bruit. Le ballon reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : mettre dans le sac. Lila répète tout bas : sac, ce que l'adulte a dit. On écoute jusqu'au bout. papa n'est pas loin.</t>
-        </is>
-      </c>
-      <c r="AX64" t="inlineStr"/>
+          <t>narrateur|Sarah monte la gourde au palier.
+narrateur|La gourde cliquette dans le sac.
+narrateur|La marche craque, tout doux.
+maman|La gourde dans le sac, Sarah.
+maman|Comme l'adulte a dit.
+narrateur|Sarah pose le cartable.
+narrateur|La gourde reste droite.
+papa|Bravo.
+papa|Tu as mis ce que maman a dit.
+maman|Elle ne tombe pas ?
+enfant-f|Non.
+narrateur|L'orange sent encore en bas.</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>escalier</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -12108,7 +12815,7 @@
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre Tom, Léa, ou Sami.</t>
+          <t>On peut prendre le crayon, le mouchoir, ou le livre.</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
@@ -12276,7 +12983,7 @@
       </c>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
+          <t>narrateur|On peut prendre le crayon, le mouchoir, ou le livre.</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr"/>
@@ -12304,7 +13011,7 @@
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>Lila rejoint Tom. Une feuille tombe. On souffle doucement. Cette fin-là est celle de les balançoires, le ballon et Tom. Lila a appris : Préparer son sac. Voici le geste : mettre dans le sac. Lila a entendu : sac, ce que l'adulte a dit. Lila dit merci à maman. On rentre.</t>
+          <t>Au palier, un crayon jaune attend. Il sent le bois. La mine est bien taillée. Le crayon dans le sac, Sarah. Le crayon. Sarah le glisse près du bord. Bravo. Tu as mis ce que maman a dit. La gourde est déjà dedans. Le sac a ce que l'adulte a dit. Tu as fini le crayon ? Oui, papa. La gourde ne cliquette plus.</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
@@ -12444,10 +13151,26 @@
       <c r="AV66" s="2" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>narrateur|Lila rejoint Tom. Une feuille tombe. On souffle doucement. Cette fin-là est celle de les balançoires, le ballon et Tom. Lila a appris : Préparer son sac. Voici le geste : mettre dans le sac. Lila a entendu : sac, ce que l'adulte a dit. Lila dit merci à maman. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX66" t="inlineStr"/>
+          <t>narrateur|Au palier, un crayon jaune attend.
+narrateur|Il sent le bois.
+narrateur|La mine est bien taillée.
+maman|Le crayon dans le sac, Sarah.
+enfant-f|Le crayon.
+narrateur|Sarah le glisse près du bord.
+papa|Bravo.
+papa|Tu as mis ce que maman a dit.
+narrateur|La gourde est déjà dedans.
+maman|Le sac a ce que l'adulte a dit.
+papa|Tu as fini le crayon ?
+enfant-f|Oui, papa.
+narrateur|La gourde ne cliquette plus.</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>crayon</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12472,7 +13195,7 @@
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Sarah ferme le sac. Ça fait zzz. Le sac est prêt. Bravo, Sarah. Tu as fait du bon travail. Tu as mis la gourde. Et le crayon. C'est ce que l'adulte a dit. Merci. Ils restent un moment près de le palier. La gourde ne cliquette plus. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
@@ -12612,7 +13335,18 @@
       <c r="AV67" s="2" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Sarah ferme le sac.
+narrateur|Ça fait zzz.
+papa|Le sac est prêt.
+maman|Bravo, Sarah.
+maman|Tu as fait du bon travail.
+papa|Tu as mis la gourde.
+maman|Et le crayon.
+papa|C'est ce que l'adulte a dit.
+enfant-f|Merci.
+narrateur|Ils restent un moment près de le palier.
+narrateur|La gourde ne cliquette plus.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr"/>
@@ -12640,7 +13374,7 @@
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>Lila rejoint Léa. L'eau coule, tout petit bruit. On écoute jusqu'au bout. Cette fin-là est celle de les balançoires, le ballon et Léa. Lila a appris : Préparer son sac. Voici le geste : mettre dans le sac. Lila a entendu : sac, ce que l'adulte a dit. Lila dit merci à maman. On rentre.</t>
+          <t>Au palier, un mouchoir propre attend. Il est doux et plié. Il sent le linge. Le mouchoir dans le sac, Sarah. Le mouchoir. Sarah le pose dans une poche. Bravo. Tu as mis ce que papa a dit. La gourde est déjà dedans. Le sac a ce que l'adulte a dit. La poche est fermée ? Oui. Une goutte a séché.</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
@@ -12780,10 +13514,26 @@
       <c r="AV68" s="2" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>narrateur|Lila rejoint Léa. L'eau coule, tout petit bruit. On écoute jusqu'au bout. Cette fin-là est celle de les balançoires, le ballon et Léa. Lila a appris : Préparer son sac. Voici le geste : mettre dans le sac. Lila a entendu : sac, ce que l'adulte a dit. Lila dit merci à maman. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX68" t="inlineStr"/>
+          <t>narrateur|Au palier, un mouchoir propre attend.
+narrateur|Il est doux et plié.
+narrateur|Il sent le linge.
+papa|Le mouchoir dans le sac, Sarah.
+enfant-f|Le mouchoir.
+narrateur|Sarah le pose dans une poche.
+maman|Bravo.
+maman|Tu as mis ce que papa a dit.
+narrateur|La gourde est déjà dedans.
+papa|Le sac a ce que l'adulte a dit.
+maman|La poche est fermée ?
+enfant-f|Oui.
+narrateur|Une goutte a séché.</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>mouchoir</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12808,7 +13558,7 @@
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Sarah ferme le sac. Ça fait zzz. Le sac est prêt. Bravo, Sarah. Tu as fait du bon travail. Tu as mis la gourde. Et le mouchoir. C'est ce que l'adulte a dit. Merci. Ils restent un moment près de le palier. Une goutte a séché sur le palier. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
@@ -12948,7 +13698,18 @@
       <c r="AV69" s="2" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Sarah ferme le sac.
+narrateur|Ça fait zzz.
+papa|Le sac est prêt.
+maman|Bravo, Sarah.
+maman|Tu as fait du bon travail.
+papa|Tu as mis la gourde.
+maman|Et le mouchoir.
+papa|C'est ce que l'adulte a dit.
+enfant-f|Merci.
+narrateur|Ils restent un moment près de le palier.
+narrateur|Une goutte a séché sur le palier.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr"/>
@@ -12976,7 +13737,7 @@
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>Lila rejoint Sami. Un vélo passe au loin. On attend son tour. Cette fin-là est celle de les balançoires, le ballon et Sami. Lila a appris : Préparer son sac. Voici le geste : mettre dans le sac. Lila a entendu : sac, ce que l'adulte a dit. Lila dit merci à maman. On rentre.</t>
+          <t>Au palier, un petit livre attend. Les pages sentent le papier. La couverture est lisse. Le livre dans le sac, Sarah. Le livre. Sarah le glisse à plat. Bravo. Tu as mis ce que maman a dit. La gourde est déjà dedans. Le sac a ce que l'adulte a dit. Le livre est à plat ? Oui, papa. Le cartable est presque prêt.</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
@@ -13116,10 +13877,26 @@
       <c r="AV70" s="2" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>narrateur|Lila rejoint Sami. Un vélo passe au loin. On attend son tour. Cette fin-là est celle de les balançoires, le ballon et Sami. Lila a appris : Préparer son sac. Voici le geste : mettre dans le sac. Lila a entendu : sac, ce que l'adulte a dit. Lila dit merci à maman. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX70" t="inlineStr"/>
+          <t>narrateur|Au palier, un petit livre attend.
+narrateur|Les pages sentent le papier.
+narrateur|La couverture est lisse.
+maman|Le livre dans le sac, Sarah.
+enfant-f|Le livre.
+narrateur|Sarah le glisse à plat.
+papa|Bravo.
+papa|Tu as mis ce que maman a dit.
+narrateur|La gourde est déjà dedans.
+maman|Le sac a ce que l'adulte a dit.
+papa|Le livre est à plat ?
+enfant-f|Oui, papa.
+narrateur|Le cartable est presque prêt.</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>livre</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -13144,7 +13921,7 @@
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Sarah ferme le sac. Ça fait zzz. Le sac est prêt. Bravo, Sarah. Tu as fait du bon travail. Tu as mis la gourde. Et le livre. C'est ce que l'adulte a dit. Merci. Ils restent un moment près de le palier. Le cartable est prêt pour l'école. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
@@ -13284,7 +14061,18 @@
       <c r="AV71" s="2" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Sarah ferme le sac.
+narrateur|Ça fait zzz.
+papa|Le sac est prêt.
+maman|Bravo, Sarah.
+maman|Tu as fait du bon travail.
+papa|Tu as mis la gourde.
+maman|Et le livre.
+papa|C'est ce que l'adulte a dit.
+enfant-f|Merci.
+narrateur|Ils restent un moment près de le palier.
+narrateur|Le cartable est prêt pour l'école.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr"/>
@@ -13312,7 +14100,7 @@
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>Lila a choisi le seau. Un vélo passe au loin. Le seau reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : mettre dans le sac. Lila répète tout bas : sac, ce que l'adulte a dit. On attend son tour. papa n'est pas loin.</t>
+          <t>Sarah accroche le sac au portemanteau. La gourde pèse d'un côté. Le crochet tient bon. La gourde dans le sac. C'est ce que l'adulte a dit. Sarah redresse le cartable. La gourde ne cliquette plus. Bravo. Tu as mis ce que papa a dit. Le sac est droit ? Oui, papa. Le portemanteau ne bouge plus.</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
@@ -13452,10 +14240,25 @@
       <c r="AV72" s="2" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>narrateur|Lila a choisi le seau. Un vélo passe au loin. Le seau reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : mettre dans le sac. Lila répète tout bas : sac, ce que l'adulte a dit. On attend son tour. papa n'est pas loin.</t>
-        </is>
-      </c>
-      <c r="AX72" t="inlineStr"/>
+          <t>narrateur|Sarah accroche le sac au portemanteau.
+narrateur|La gourde pèse d'un côté.
+narrateur|Le crochet tient bon.
+papa|La gourde dans le sac.
+papa|C'est ce que l'adulte a dit.
+narrateur|Sarah redresse le cartable.
+narrateur|La gourde ne cliquette plus.
+maman|Bravo.
+maman|Tu as mis ce que papa a dit.
+papa|Le sac est droit ?
+enfant-f|Oui, papa.
+narrateur|Le portemanteau ne bouge plus.</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>crochet</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13480,7 +14283,7 @@
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre Tom, Léa, ou Sami.</t>
+          <t>On peut prendre le crayon, le mouchoir, ou le livre.</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr">
@@ -13648,7 +14451,7 @@
       </c>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
+          <t>narrateur|On peut prendre le crayon, le mouchoir, ou le livre.</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr"/>
@@ -13676,7 +14479,7 @@
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>Lila rejoint Tom. L'eau coule, tout petit bruit. On souffle doucement. Cette fin-là est celle de les balançoires, le seau et Tom. Lila a appris : Préparer son sac. Voici le geste : mettre dans le sac. Lila a entendu : sac, ce que l'adulte a dit. Lila dit merci à maman. On rentre.</t>
+          <t>Au portemanteau, un crayon jaune attend. Il sent le bois. La mine est bien taillée. Le crayon dans le sac, Sarah. Le crayon. Sarah le glisse près du bord. Bravo. Tu as mis ce que maman a dit. La gourde est déjà dedans. Le sac a ce que l'adulte a dit. Tu as fini le crayon ? Oui, papa. Le bouchon tient bien.</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
@@ -13816,10 +14619,26 @@
       <c r="AV74" s="2" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>narrateur|Lila rejoint Tom. L'eau coule, tout petit bruit. On souffle doucement. Cette fin-là est celle de les balançoires, le seau et Tom. Lila a appris : Préparer son sac. Voici le geste : mettre dans le sac. Lila a entendu : sac, ce que l'adulte a dit. Lila dit merci à maman. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX74" t="inlineStr"/>
+          <t>narrateur|Au portemanteau, un crayon jaune attend.
+narrateur|Il sent le bois.
+narrateur|La mine est bien taillée.
+maman|Le crayon dans le sac, Sarah.
+enfant-f|Le crayon.
+narrateur|Sarah le glisse près du bord.
+papa|Bravo.
+papa|Tu as mis ce que maman a dit.
+narrateur|La gourde est déjà dedans.
+maman|Le sac a ce que l'adulte a dit.
+papa|Tu as fini le crayon ?
+enfant-f|Oui, papa.
+narrateur|Le bouchon tient bien.</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>crayon</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13844,7 +14663,7 @@
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Sarah ferme le sac. Ça fait zzz. Le sac est prêt. Bravo, Sarah. Tu as fait du bon travail. Tu as mis la gourde. Et le crayon. C'est ce que l'adulte a dit. Merci. Ils restent un moment près de le portemanteau. Le bouchon de la gourde tient bien. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr">
@@ -13984,7 +14803,18 @@
       <c r="AV75" s="2" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Sarah ferme le sac.
+narrateur|Ça fait zzz.
+papa|Le sac est prêt.
+maman|Bravo, Sarah.
+maman|Tu as fait du bon travail.
+papa|Tu as mis la gourde.
+maman|Et le crayon.
+papa|C'est ce que l'adulte a dit.
+enfant-f|Merci.
+narrateur|Ils restent un moment près de le portemanteau.
+narrateur|Le bouchon de la gourde tient bien.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr"/>
@@ -14012,7 +14842,7 @@
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>Lila rejoint Léa. Un vélo passe au loin. On écoute jusqu'au bout. Cette fin-là est celle de les balançoires, le seau et Léa. Lila a appris : Préparer son sac. Voici le geste : mettre dans le sac. Lila a entendu : sac, ce que l'adulte a dit. Lila dit merci à maman. On rentre.</t>
+          <t>Au portemanteau, un mouchoir propre attend. Il est doux et plié. Il sent le linge. Le mouchoir dans le sac, Sarah. Le mouchoir. Sarah le pose dans une poche. Bravo. Tu as mis ce que papa a dit. La gourde est déjà dedans. Le sac a ce que l'adulte a dit. La poche est fermée ? Oui. Le portemanteau reste calme.</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
@@ -14152,10 +14982,26 @@
       <c r="AV76" s="2" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>narrateur|Lila rejoint Léa. Un vélo passe au loin. On écoute jusqu'au bout. Cette fin-là est celle de les balançoires, le seau et Léa. Lila a appris : Préparer son sac. Voici le geste : mettre dans le sac. Lila a entendu : sac, ce que l'adulte a dit. Lila dit merci à maman. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX76" t="inlineStr"/>
+          <t>narrateur|Au portemanteau, un mouchoir propre attend.
+narrateur|Il est doux et plié.
+narrateur|Il sent le linge.
+papa|Le mouchoir dans le sac, Sarah.
+enfant-f|Le mouchoir.
+narrateur|Sarah le pose dans une poche.
+maman|Bravo.
+maman|Tu as mis ce que papa a dit.
+narrateur|La gourde est déjà dedans.
+papa|Le sac a ce que l'adulte a dit.
+maman|La poche est fermée ?
+enfant-f|Oui.
+narrateur|Le portemanteau reste calme.</t>
+        </is>
+      </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>mouchoir</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -14180,7 +15026,7 @@
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Sarah ferme le sac. Ça fait zzz. Le sac est prêt. Bravo, Sarah. Tu as fait du bon travail. Tu as mis la gourde. Et le mouchoir. C'est ce que l'adulte a dit. Merci. Ils restent un moment près de le portemanteau. Le portemanteau ne bouge plus. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr">
@@ -14320,7 +15166,18 @@
       <c r="AV77" s="2" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Sarah ferme le sac.
+narrateur|Ça fait zzz.
+papa|Le sac est prêt.
+maman|Bravo, Sarah.
+maman|Tu as fait du bon travail.
+papa|Tu as mis la gourde.
+maman|Et le mouchoir.
+papa|C'est ce que l'adulte a dit.
+enfant-f|Merci.
+narrateur|Ils restent un moment près de le portemanteau.
+narrateur|Le portemanteau ne bouge plus.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr"/>
@@ -14348,7 +15205,7 @@
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>Lila rejoint Sami. La lumière est claire. On attend son tour. Cette fin-là est celle de les balançoires, le seau et Sami. Lila a appris : Préparer son sac. Voici le geste : mettre dans le sac. Lila a entendu : sac, ce que l'adulte a dit. Lila dit merci à maman. On rentre.</t>
+          <t>Au portemanteau, un petit livre attend. Les pages sentent le papier. La couverture est lisse. Le livre dans le sac, Sarah. Le livre. Sarah le glisse à plat. Bravo. Tu as mis ce que maman a dit. La gourde est déjà dedans. Le sac a ce que l'adulte a dit. Le livre est à plat ? Oui, papa. Sarah touche la boucle.</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
@@ -14488,10 +15345,26 @@
       <c r="AV78" s="2" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>narrateur|Lila rejoint Sami. La lumière est claire. On attend son tour. Cette fin-là est celle de les balançoires, le seau et Sami. Lila a appris : Préparer son sac. Voici le geste : mettre dans le sac. Lila a entendu : sac, ce que l'adulte a dit. Lila dit merci à maman. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX78" t="inlineStr"/>
+          <t>narrateur|Au portemanteau, un petit livre attend.
+narrateur|Les pages sentent le papier.
+narrateur|La couverture est lisse.
+maman|Le livre dans le sac, Sarah.
+enfant-f|Le livre.
+narrateur|Sarah le glisse à plat.
+papa|Bravo.
+papa|Tu as mis ce que maman a dit.
+narrateur|La gourde est déjà dedans.
+maman|Le sac a ce que l'adulte a dit.
+papa|Le livre est à plat ?
+enfant-f|Oui, papa.
+narrateur|Sarah touche la boucle.</t>
+        </is>
+      </c>
+      <c r="AX78" t="inlineStr">
+        <is>
+          <t>livre</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14516,7 +15389,7 @@
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Sarah ferme le sac. Ça fait zzz. Le sac est prêt. Bravo, Sarah. Tu as fait du bon travail. Tu as mis la gourde. Et le livre. C'est ce que l'adulte a dit. Merci. Ils restent un moment près de le portemanteau. Sarah touche encore la boucle. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F79" s="2" t="inlineStr">
@@ -14656,7 +15529,18 @@
       <c r="AV79" s="2" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Sarah ferme le sac.
+narrateur|Ça fait zzz.
+papa|Le sac est prêt.
+maman|Bravo, Sarah.
+maman|Tu as fait du bon travail.
+papa|Tu as mis la gourde.
+maman|Et le livre.
+papa|C'est ce que l'adulte a dit.
+enfant-f|Merci.
+narrateur|Ils restent un moment près de le portemanteau.
+narrateur|Sarah touche encore la boucle.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr"/>
@@ -14684,7 +15568,7 @@
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>Lila a choisi le doudou. La lumière est claire. Le doudou reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : mettre dans le sac. Lila répète tout bas : sac, ce que l'adulte a dit. On montre du doigt, sans courir. papa n'est pas loin.</t>
+          <t>Sarah pose le sac sur le banc. La gourde fait un petit clic. Le soleil touche le bouchon. La gourde dans le sac, Sarah. Comme l'adulte a dit. Sarah pousse le sac au milieu. La gourde reste au fond. Bravo. Tu as mis ce que maman a dit. Tu as fini sur le banc ? Oui. Le rectangle de soleil a bougé.</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
@@ -14824,10 +15708,25 @@
       <c r="AV80" s="2" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>narrateur|Lila a choisi le doudou. La lumière est claire. Le doudou reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : mettre dans le sac. Lila répète tout bas : sac, ce que l'adulte a dit. On montre du doigt, sans courir. papa n'est pas loin.</t>
-        </is>
-      </c>
-      <c r="AX80" t="inlineStr"/>
+          <t>narrateur|Sarah pose le sac sur le banc.
+narrateur|La gourde fait un petit clic.
+narrateur|Le soleil touche le bouchon.
+maman|La gourde dans le sac, Sarah.
+maman|Comme l'adulte a dit.
+narrateur|Sarah pousse le sac au milieu.
+narrateur|La gourde reste au fond.
+papa|Bravo.
+papa|Tu as mis ce que maman a dit.
+maman|Tu as fini sur le banc ?
+enfant-f|Oui.
+narrateur|Le rectangle de soleil a bougé.</t>
+        </is>
+      </c>
+      <c r="AX80" t="inlineStr">
+        <is>
+          <t>banc</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14852,7 +15751,7 @@
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre Tom, Léa, ou Sami.</t>
+          <t>On peut prendre le crayon, le mouchoir, ou le livre.</t>
         </is>
       </c>
       <c r="F81" s="2" t="inlineStr">
@@ -15020,7 +15919,7 @@
       </c>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
+          <t>narrateur|On peut prendre le crayon, le mouchoir, ou le livre.</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr"/>
@@ -15048,7 +15947,7 @@
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>Lila rejoint Tom. Un vélo passe au loin. On souffle doucement. Cette fin-là est celle de les balançoires, le doudou et Tom. Lila a appris : Préparer son sac. Voici le geste : mettre dans le sac. Lila a entendu : sac, ce que l'adulte a dit. Lila dit merci à maman. On rentre.</t>
+          <t>Sur le banc, un crayon jaune attend. Il sent le bois. La mine est bien taillée. Le crayon dans le sac, Sarah. Le crayon. Sarah le glisse près du bord. Bravo. Tu as mis ce que maman a dit. La gourde est déjà dedans. Le sac a ce que l'adulte a dit. Tu as fini le crayon ? Oui, papa. Le rectangle de soleil a bougé.</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr">
@@ -15188,10 +16087,26 @@
       <c r="AV82" s="2" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>narrateur|Lila rejoint Tom. Un vélo passe au loin. On souffle doucement. Cette fin-là est celle de les balançoires, le doudou et Tom. Lila a appris : Préparer son sac. Voici le geste : mettre dans le sac. Lila a entendu : sac, ce que l'adulte a dit. Lila dit merci à maman. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX82" t="inlineStr"/>
+          <t>narrateur|Sur le banc, un crayon jaune attend.
+narrateur|Il sent le bois.
+narrateur|La mine est bien taillée.
+maman|Le crayon dans le sac, Sarah.
+enfant-f|Le crayon.
+narrateur|Sarah le glisse près du bord.
+papa|Bravo.
+papa|Tu as mis ce que maman a dit.
+narrateur|La gourde est déjà dedans.
+maman|Le sac a ce que l'adulte a dit.
+papa|Tu as fini le crayon ?
+enfant-f|Oui, papa.
+narrateur|Le rectangle de soleil a bougé.</t>
+        </is>
+      </c>
+      <c r="AX82" t="inlineStr">
+        <is>
+          <t>crayon</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -15216,7 +16131,7 @@
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Sarah ferme le sac. Ça fait zzz. Le sac est prêt. Bravo, Sarah. Tu as fait du bon travail. Tu as mis la gourde. Et le crayon. C'est ce que l'adulte a dit. Merci. Ils restent un moment près de le banc. Le rectangle de soleil a disparu. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F83" s="2" t="inlineStr">
@@ -15356,7 +16271,18 @@
       <c r="AV83" s="2" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Sarah ferme le sac.
+narrateur|Ça fait zzz.
+papa|Le sac est prêt.
+maman|Bravo, Sarah.
+maman|Tu as fait du bon travail.
+papa|Tu as mis la gourde.
+maman|Et le crayon.
+papa|C'est ce que l'adulte a dit.
+enfant-f|Merci.
+narrateur|Ils restent un moment près de le banc.
+narrateur|Le rectangle de soleil a disparu.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr"/>
@@ -15384,7 +16310,7 @@
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>Lila rejoint Léa. La lumière est claire. On écoute jusqu'au bout. Cette fin-là est celle de les balançoires, le doudou et Léa. Lila a appris : Préparer son sac. Voici le geste : mettre dans le sac. Lila a entendu : sac, ce que l'adulte a dit. Lila dit merci à maman. On rentre.</t>
+          <t>Sur le banc, un mouchoir propre attend. Il est doux et plié. Il sent le linge. Le mouchoir dans le sac, Sarah. Le mouchoir. Sarah le pose dans une poche. Bravo. Tu as mis ce que papa a dit. La gourde est déjà dedans. Le sac a ce que l'adulte a dit. La poche est fermée ? Oui. Le banc est tiède.</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr">
@@ -15524,10 +16450,26 @@
       <c r="AV84" s="2" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>narrateur|Lila rejoint Léa. La lumière est claire. On écoute jusqu'au bout. Cette fin-là est celle de les balançoires, le doudou et Léa. Lila a appris : Préparer son sac. Voici le geste : mettre dans le sac. Lila a entendu : sac, ce que l'adulte a dit. Lila dit merci à maman. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX84" t="inlineStr"/>
+          <t>narrateur|Sur le banc, un mouchoir propre attend.
+narrateur|Il est doux et plié.
+narrateur|Il sent le linge.
+papa|Le mouchoir dans le sac, Sarah.
+enfant-f|Le mouchoir.
+narrateur|Sarah le pose dans une poche.
+maman|Bravo.
+maman|Tu as mis ce que papa a dit.
+narrateur|La gourde est déjà dedans.
+papa|Le sac a ce que l'adulte a dit.
+maman|La poche est fermée ?
+enfant-f|Oui.
+narrateur|Le banc est tiède.</t>
+        </is>
+      </c>
+      <c r="AX84" t="inlineStr">
+        <is>
+          <t>mouchoir</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15552,7 +16494,7 @@
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Sarah ferme le sac. Ça fait zzz. Le sac est prêt. Bravo, Sarah. Tu as fait du bon travail. Tu as mis la gourde. Et le mouchoir. C'est ce que l'adulte a dit. Merci. Ils restent un moment près de le banc. Le banc est tiède sous le sac. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F85" s="2" t="inlineStr">
@@ -15692,7 +16634,18 @@
       <c r="AV85" s="2" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Sarah ferme le sac.
+narrateur|Ça fait zzz.
+papa|Le sac est prêt.
+maman|Bravo, Sarah.
+maman|Tu as fait du bon travail.
+papa|Tu as mis la gourde.
+maman|Et le mouchoir.
+papa|C'est ce que l'adulte a dit.
+enfant-f|Merci.
+narrateur|Ils restent un moment près de le banc.
+narrateur|Le banc est tiède sous le sac.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr"/>
@@ -15720,7 +16673,7 @@
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>Lila rejoint Sami. Il y a des miettes sur la table. On attend son tour. Cette fin-là est celle de les balançoires, le doudou et Sami. Lila a appris : Préparer son sac. Voici le geste : mettre dans le sac. Lila a entendu : sac, ce que l'adulte a dit. Lila dit merci à maman. On rentre.</t>
+          <t>Sur le banc, un petit livre attend. Les pages sentent le papier. La couverture est lisse. Le livre dans le sac, Sarah. Le livre. Sarah le glisse à plat. Bravo. Tu as mis ce que maman a dit. La gourde est déjà dedans. Le sac a ce que l'adulte a dit. Le livre est à plat ? Oui, papa. Loin, la cloche se tait.</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr">
@@ -15860,10 +16813,26 @@
       <c r="AV86" s="2" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>narrateur|Lila rejoint Sami. Il y a des miettes sur la table. On attend son tour. Cette fin-là est celle de les balançoires, le doudou et Sami. Lila a appris : Préparer son sac. Voici le geste : mettre dans le sac. Lila a entendu : sac, ce que l'adulte a dit. Lila dit merci à maman. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX86" t="inlineStr"/>
+          <t>narrateur|Sur le banc, un petit livre attend.
+narrateur|Les pages sentent le papier.
+narrateur|La couverture est lisse.
+maman|Le livre dans le sac, Sarah.
+enfant-f|Le livre.
+narrateur|Sarah le glisse à plat.
+papa|Bravo.
+papa|Tu as mis ce que maman a dit.
+narrateur|La gourde est déjà dedans.
+maman|Le sac a ce que l'adulte a dit.
+papa|Le livre est à plat ?
+enfant-f|Oui, papa.
+narrateur|Loin, la cloche se tait.</t>
+        </is>
+      </c>
+      <c r="AX86" t="inlineStr">
+        <is>
+          <t>livre</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15888,7 +16857,7 @@
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Sarah ferme le sac. Ça fait zzz. Le sac est prêt. Bravo, Sarah. Tu as fait du bon travail. Tu as mis la gourde. Et le livre. C'est ce que l'adulte a dit. Merci. Ils restent un moment près de le banc. Loin, la cloche de l'école se tait. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F87" s="2" t="inlineStr">
@@ -16028,7 +16997,18 @@
       <c r="AV87" s="2" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Sarah ferme le sac.
+narrateur|Ça fait zzz.
+papa|Le sac est prêt.
+maman|Bravo, Sarah.
+maman|Tu as fait du bon travail.
+papa|Tu as mis la gourde.
+maman|Et le livre.
+papa|C'est ce que l'adulte a dit.
+enfant-f|Merci.
+narrateur|Ils restent un moment près de le banc.
+narrateur|Loin, la cloche de l'école se tait.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr"/>
@@ -16050,7 +17030,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A13"/>
+  <dimension ref="A1:A14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -16144,6 +17124,13 @@
       <c r="A13" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>
